--- a/data/merged/2026-09-28/MERGED_FR_Spot-Cleaner_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_FR_Spot-Cleaner_2026-09-28.xlsx
@@ -7239,13 +7239,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7283,13 +7283,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7718,94 +7718,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8131,7 +8043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16390,295 +16302,35 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0FFHS6LWS</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Style: 15cm</t>
+          <t>Set name: Aspirateur Balai Sans Fil (350W)</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Marque: Bissell | Couleur: Multicolore | Style: 15cm | Nom de modèle: 2365 | Source d'alimentation: Avec cordon secteur | Nombre d'unités: 1.0 unité | Fabricant: BISSELL | Code article international: 00011120244618 | UPC: 011120244618 | Nombre d'articles: 1</t>
+          <t>Marque: Olvy | Type de filtre: Filtre HEPA | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Composants inclus: Aspirateur à main, Suceur plat, Brosse 2-en-1, Brosse à sol, Support mural, Serpillière | Sans fil ?: Oui | Utilisations recommandées pour le produit: Nettoyage de tapis, sols durs, canapés, zones difficiles d’accès, enlèvement des poils d’animaux | Facteur de forme: Bâton | Couleur: Bleu Foncé | Nom de modèle: Olvy Turbo-A10</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Bissell Brosse pour Taches Tenaces, Noir, 15 cm</t>
+          <t>Olvy Aspirateur Balai sans Fil Nettoyeur Puissant 350W Dark Blue 35KPa Pure</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>L'outil idéal pour toutes les shampouineuses à moquette et les détacheurs Bissell
-Fixez la brosse au tuyau de votre shampouineuse à moquette verticale ou détacheur portable Bissell pour utiliser sur les taches difficiles à enlever
-Idéale pour nettoyer les escaliers, les meubles, et d'autres surfaces difficiles à atteindre
-La brosse à taches extra large aide à enlever même les taches les plus tenaces
-Buse amovible pour un nettoyage facile après utilisation</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B07999DC2C?psc=1</t>
-        </is>
-      </c>
-      <c r="K34" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L34" s="14" t="inlineStr">
-        <is>
-          <t>B09XN93JDC</t>
-        </is>
-      </c>
-      <c r="M34" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O34" s="15">
-        <v>2406</v>
-      </c>
-      <c r="P34" s="15">
-        <v>361</v>
-      </c>
-      <c r="Q34" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="R34" s="17" t="inlineStr">
-        <is>
-          <t>Accessoires pour nettoyeurs vapeur
-Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S34" s="18" t="inlineStr">
-        <is>
-          <t>4
-17</t>
-        </is>
-      </c>
-      <c r="T34" s="15">
-        <v>337</v>
-      </c>
-      <c r="U34" s="16">
-        <v>0.24</v>
-      </c>
-      <c r="V34" s="15">
-        <v>8422</v>
-      </c>
-      <c r="W34" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X34" s="15">
-        <v>1323</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>6</v>
-      </c>
-      <c r="Z34" s="20">
-        <v>20.82</v>
-      </c>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="2">
-        <v>4</v>
-      </c>
-      <c r="AD34" s="19">
-        <v>1385</v>
-      </c>
-      <c r="AE34" s="15">
-        <v>14</v>
-      </c>
-      <c r="AF34" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG34" s="22">
-        <v>0.0415</v>
-      </c>
-      <c r="AH34" s="20">
-        <v>5.15</v>
-      </c>
-      <c r="AI34" s="16">
-        <v>0.64</v>
-      </c>
-      <c r="AJ34"/>
-      <c r="AK34" s="13" t="inlineStr">
-        <is>
-          <t>2018-06-01</t>
-        </is>
-      </c>
-      <c r="AL34" s="19">
-        <v>3041</v>
-      </c>
-      <c r="AM34" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN34" s="13" t="inlineStr">
-        <is>
-          <t>11天</t>
-        </is>
-      </c>
-      <c r="AO34" s="13"/>
-      <c r="AP34" s="20">
-        <v>13.61</v>
-      </c>
-      <c r="AQ34" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR34" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS34" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT34" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
-      <c r="AX34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AY34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ34" s="13"/>
-      <c r="BA34" s="13"/>
-      <c r="BB34" s="13"/>
-      <c r="BC34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE34" s="13"/>
-      <c r="BF34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG34" s="13"/>
-      <c r="BH34" s="14"/>
-      <c r="BI34" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
-      <c r="BJ34" s="23" t="inlineStr">
-        <is>
-          <t>137 g</t>
-        </is>
-      </c>
-      <c r="BK34" s="23" t="inlineStr">
-        <is>
-          <t>137.00 g</t>
-        </is>
-      </c>
-      <c r="BL34" s="23" t="inlineStr">
-        <is>
-          <t>40 x 25 x 15 cm</t>
-        </is>
-      </c>
-      <c r="BM34" s="23" t="inlineStr">
-        <is>
-          <t>40.00 x 25.00 x 15.00 cm</t>
-        </is>
-      </c>
-      <c r="BN34" s="23" t="inlineStr">
-        <is>
-          <t>150 g</t>
-        </is>
-      </c>
-      <c r="BO34" s="23" t="inlineStr">
-        <is>
-          <t>150.00 g</t>
-        </is>
-      </c>
-      <c r="BP34" s="23" t="inlineStr">
-        <is>
-          <t>16.5 x 15 x 7.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ34" s="23" t="inlineStr">
-        <is>
-          <t>16.50 x 15.00 x 7.30 cm</t>
-        </is>
-      </c>
-      <c r="BR34" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>34</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>B0FFHS6LWS</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Set name: Aspirateur Balai Sans Fil (350W)</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Marque: Olvy | Type de filtre: Filtre HEPA | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Composants inclus: Aspirateur à main, Suceur plat, Brosse 2-en-1, Brosse à sol, Support mural, Serpillière | Sans fil ?: Oui | Utilisations recommandées pour le produit: Nettoyage de tapis, sols durs, canapés, zones difficiles d’accès, enlèvement des poils d’animaux | Facteur de forme: Bâton | Couleur: Bleu Foncé | Nom de modèle: Olvy Turbo-A10</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>Olvy</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>Olvy Aspirateur Balai sans Fil Nettoyeur Puissant 350W Dark Blue 35KPa Pure</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>ASPIRATION PUISSANTE 35KPA: Moteur performant de 350W éliminant la poussière les cheveux et les débris sur carrelage parquet et tapis pour un nettoyage en profondeur de votre maison
 NETTOYAGE DOUBLE ACTION: Combinaison pratique de l'aspiration et du lavage des sols d'appoint permettant de dépoussiérer et d'essuyer vos surfaces en une seule étape pour gagner du temps
@@ -16687,19 +16339,263 @@
 ENTRETIEN DU SYSTÈME: Pour garantir une aspiration optimale veillez à vider le bac à poussière et à nettoyer fréquemment les filtres HEPA ainsi que la brosse rotative après chaque usage</t>
         </is>
       </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>B0HD1BJXTZ</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O34" s="15">
+        <v>25848</v>
+      </c>
+      <c r="P34" s="15">
+        <v>-2542</v>
+      </c>
+      <c r="Q34" s="16">
+        <v>-0.07</v>
+      </c>
+      <c r="R34" s="17" t="inlineStr">
+        <is>
+          <t>Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="S34" s="18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="T34" s="15">
+        <v>76</v>
+      </c>
+      <c r="U34" s="16">
+        <v>-0.32</v>
+      </c>
+      <c r="V34" s="15">
+        <v>6839</v>
+      </c>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="19">
+        <v>4</v>
+      </c>
+      <c r="Z34" s="20">
+        <v>89.99</v>
+      </c>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="19">
+        <v>280</v>
+      </c>
+      <c r="AE34" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="21">
+        <v>4</v>
+      </c>
+      <c r="AG34" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="20">
+        <v>8.44</v>
+      </c>
+      <c r="AI34" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="AJ34"/>
+      <c r="AK34" s="13" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AL34" s="19">
+        <v>452</v>
+      </c>
+      <c r="AM34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN34" s="13"/>
+      <c r="AO34" s="13"/>
+      <c r="AP34" s="20"/>
+      <c r="AQ34" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR34" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS34" s="14" t="inlineStr">
+        <is>
+          <t>Olvy</t>
+        </is>
+      </c>
+      <c r="AT34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>NIJMEGEN Gelderland 6511DX NL</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
+        </is>
+      </c>
+      <c r="AX34" s="13"/>
+      <c r="AY34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ34" s="13"/>
+      <c r="BA34" s="13"/>
+      <c r="BB34" s="13"/>
+      <c r="BC34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE34" s="13"/>
+      <c r="BF34" s="13"/>
+      <c r="BG34" s="13"/>
+      <c r="BH34" s="14"/>
+      <c r="BI34" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
+      <c r="BJ34" s="23" t="inlineStr">
+        <is>
+          <t>3,86 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK34" s="23" t="inlineStr">
+        <is>
+          <t>3.86 kg</t>
+        </is>
+      </c>
+      <c r="BL34" s="23" t="inlineStr">
+        <is>
+          <t>23L x 25l x 11,8H centimètres</t>
+        </is>
+      </c>
+      <c r="BM34" s="23"/>
+      <c r="BN34" s="23" t="inlineStr">
+        <is>
+          <t>3.86 kg</t>
+        </is>
+      </c>
+      <c r="BO34" s="23" t="inlineStr">
+        <is>
+          <t>3.86 kg</t>
+        </is>
+      </c>
+      <c r="BP34" s="23" t="inlineStr">
+        <is>
+          <t>44.8 x 26.3 x 19.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ34" s="23" t="inlineStr">
+        <is>
+          <t>44.80 x 26.30 x 19.90 cm</t>
+        </is>
+      </c>
+      <c r="BR34" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13">
+        <v>34</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>B0FH4QL9GN</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Set name: CM001 Plus</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Marque: Livatro | Couleur: Cm001 Plus | Poids de l'article: 3,8 Kilogrammes | Dimensions du produit: 22,9P x 37l x 35,6H centimètres | Style: Moderne | Nom de modèle: LVCUCM001 | Capacité: 2,3 litres | Source d'alimentation: Câble électrique | Fabricant: Livatro | UPC: 850057188233</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Livatro</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et Tapis</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Nettoyage en profondeur 3-en-1 : Cette shampouineuse canapé combine pulvérisation, brossage et aspiration en une seule étape pour nettoyer efficacement les tissus d’ameublement. Équipée d’un moteur haute performance de 600 W, d’une tête de brossage jusqu’à 38 000 tr/min et d’une aspiration puissante de 16 kPa, elle aide à éliminer les taches tenaces comme l’urine d’animaux, le café ou le vin rouge. Idéale pour canapés, tapis, moquettes, sièges auto et textiles du quotidien.
+Grand double réservoir pour un nettoyage hygiénique : Ce nettoyeur textile dispose d’un réservoir d’eau propre de 2,3 L et d’un réservoir d’eaux usées de 1,3 L, permettant de séparer l’eau propre de l’eau sale pour une utilisation plus hygiénique. Grâce à sa forte puissance d’aspiration, il récupère jusqu’à 90 % de l’eau, aidant les surfaces à sécher plus rapidement. Le système de verrouillage sécurisé limite efficacement les risques de fuite, même lors des déplacements.
+Léger, maniable et pratique dans toute la maison : Avec un poids d’environ 3,8 kg, cette shampouineuse voiture est facile à transporter d’une pièce à l’autre. Son câble d’alimentation de 5 m et son flexible de 1,28 m offrent un rayon d’action d’environ 6,3 m, idéal pour atteindre facilement les zones difficiles comme les interstices de canapé, les escaliers, les coins étroits ou l’intérieur des véhicules.
+Set de brosses professionnel pour plusieurs surfaces : Livré avec une brosse multifonction et une brosse d’angle pour interstices, cet aspirateur laveur textile s’adapte à différents besoins de nettoyage. La brosse multifonction convient aux surfaces plus larges comme les canapés, tapis, moquettes, escaliers, sièges auto et paniers pour animaux. La brosse d’angle permet d’atteindre les bords de meubles, les coins profonds et les espaces étroits de l’habitacle.
+Auto-nettoyage en un seul bouton : Après utilisation, la fonction d’auto-nettoyage lance automatiquement le rinçage des conduits d’une simple pression. Elle aide à réduire les résidus, les obstructions et les mauvaises odeurs, pour garder l’appareil plus propre après chaque nettoyage. Les réservoirs amovibles facilitent le remplissage, la vidange et l’entretien quotidien.</t>
+        </is>
+      </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0HD1BJXTZ</t>
+          <t>B0HBPKX2KK</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -16713,13 +16609,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>25848</v>
+        <v>22078</v>
       </c>
       <c r="P35" s="15">
-        <v>-2542</v>
+        <v>-12016</v>
       </c>
       <c r="Q35" s="16">
-        <v>-0.07</v>
+        <v>-0.4</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -16728,55 +16624,61 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="U35" s="16">
-        <v>-0.32</v>
+        <v>0.08</v>
       </c>
       <c r="V35" s="15">
-        <v>6839</v>
-      </c>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
+        <v>6280</v>
+      </c>
+      <c r="W35" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X35" s="15">
+        <v>3795</v>
+      </c>
       <c r="Y35" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>89.99</v>
+        <v>72.18</v>
       </c>
       <c r="AA35" s="4"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="AE35" s="15">
         <v>0</v>
       </c>
       <c r="AF35" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
       <c r="AH35" s="20">
-        <v>8.44</v>
+        <v>8.68</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>452</v>
+        <v>398</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -16794,7 +16696,7 @@
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>Kayon International</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -16804,17 +16706,17 @@
       </c>
       <c r="AU35" s="13" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>NIJMEGEN Gelderland 6511DX NL</t>
+          <t>HONGKONG 999077 HK</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
@@ -16837,7 +16739,11 @@
         </is>
       </c>
       <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
+      <c r="BF35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
       <c r="BI35" s="23" t="inlineStr">
@@ -16847,43 +16753,39 @@
       </c>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>3,86 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK35" s="23" t="inlineStr">
-        <is>
-          <t>3.86 kg</t>
-        </is>
-      </c>
+          <t>3,8 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK35" s="23"/>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>23L x 25l x 11,8H centimètres</t>
+          <t>22,9P x 37l x 35,6H centimètres</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>44.8 x 26.3 x 19.9 cm</t>
+          <t>45.1 x 36.6 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>44.80 x 26.30 x 19.90 cm</t>
+          <t>45.10 x 36.60 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16894,281 +16796,31 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Set name: CM001 Plus</t>
-        </is>
-      </c>
+          <t>B01HZUX61M</t>
+        </is>
+      </c>
+      <c r="D36" s="14"/>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Marque: Livatro | Couleur: Cm001 Plus | Poids de l'article: 3,8 Kilogrammes | Dimensions du produit: 22,9P x 37l x 35,6H centimètres | Style: Moderne | Nom de modèle: LVCUCM001 | Capacité: 2,3 litres | Source d'alimentation: Câble électrique | Fabricant: Livatro | UPC: 850057188233</t>
+          <t>Marque: Tech'N'Fast | Forme de l'article: Liquide | Parfum: Lavande | Usages spécifiques pour le produit: Moquette | Caractéristique du matériau: Biodégradable | Nombre d'unités: 5000.00 millilitre</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>Tech'N'Fast</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et Tapis</t>
+          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - Bidon 5L- pulvérisateur 600 ml offert</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>Nettoyage en profondeur 3-en-1 : Cette shampouineuse canapé combine pulvérisation, brossage et aspiration en une seule étape pour nettoyer efficacement les tissus d’ameublement. Équipée d’un moteur haute performance de 600 W, d’une tête de brossage jusqu’à 38 000 tr/min et d’une aspiration puissante de 16 kPa, elle aide à éliminer les taches tenaces comme l’urine d’animaux, le café ou le vin rouge. Idéale pour canapés, tapis, moquettes, sièges auto et textiles du quotidien.
-Grand double réservoir pour un nettoyage hygiénique : Ce nettoyeur textile dispose d’un réservoir d’eau propre de 2,3 L et d’un réservoir d’eaux usées de 1,3 L, permettant de séparer l’eau propre de l’eau sale pour une utilisation plus hygiénique. Grâce à sa forte puissance d’aspiration, il récupère jusqu’à 90 % de l’eau, aidant les surfaces à sécher plus rapidement. Le système de verrouillage sécurisé limite efficacement les risques de fuite, même lors des déplacements.
-Léger, maniable et pratique dans toute la maison : Avec un poids d’environ 3,8 kg, cette shampouineuse voiture est facile à transporter d’une pièce à l’autre. Son câble d’alimentation de 5 m et son flexible de 1,28 m offrent un rayon d’action d’environ 6,3 m, idéal pour atteindre facilement les zones difficiles comme les interstices de canapé, les escaliers, les coins étroits ou l’intérieur des véhicules.
-Set de brosses professionnel pour plusieurs surfaces : Livré avec une brosse multifonction et une brosse d’angle pour interstices, cet aspirateur laveur textile s’adapte à différents besoins de nettoyage. La brosse multifonction convient aux surfaces plus larges comme les canapés, tapis, moquettes, escaliers, sièges auto et paniers pour animaux. La brosse d’angle permet d’atteindre les bords de meubles, les coins profonds et les espaces étroits de l’habitacle.
-Auto-nettoyage en un seul bouton : Après utilisation, la fonction d’auto-nettoyage lance automatiquement le rinçage des conduits d’une simple pression. Elle aide à réduire les résidus, les obstructions et les mauvaises odeurs, pour garder l’appareil plus propre après chaque nettoyage. Les réservoirs amovibles facilitent le remplissage, la vidange et l’entretien quotidien.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>B0HBPKX2KK</t>
-        </is>
-      </c>
-      <c r="M36" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O36" s="15">
-        <v>22078</v>
-      </c>
-      <c r="P36" s="15">
-        <v>-12016</v>
-      </c>
-      <c r="Q36" s="16">
-        <v>-0.4</v>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S36" s="18" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="T36" s="15">
-        <v>87</v>
-      </c>
-      <c r="U36" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="V36" s="15">
-        <v>6280</v>
-      </c>
-      <c r="W36" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X36" s="15">
-        <v>3795</v>
-      </c>
-      <c r="Y36" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="20">
-        <v>72.18</v>
-      </c>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="19">
-        <v>306</v>
-      </c>
-      <c r="AE36" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="20">
-        <v>8.68</v>
-      </c>
-      <c r="AI36" s="16">
-        <v>0.73</v>
-      </c>
-      <c r="AJ36"/>
-      <c r="AK36" s="13" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AL36" s="19">
-        <v>398</v>
-      </c>
-      <c r="AM36" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN36" s="13"/>
-      <c r="AO36" s="13"/>
-      <c r="AP36" s="20"/>
-      <c r="AQ36" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR36" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS36" s="14" t="inlineStr">
-        <is>
-          <t>Kayon International</t>
-        </is>
-      </c>
-      <c r="AT36" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU36" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV36" s="14" t="inlineStr">
-        <is>
-          <t>HONGKONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW36" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
-        </is>
-      </c>
-      <c r="AX36" s="13"/>
-      <c r="AY36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
-      <c r="BB36" s="13"/>
-      <c r="BC36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE36" s="13"/>
-      <c r="BF36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG36" s="13"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
-      <c r="BJ36" s="23" t="inlineStr">
-        <is>
-          <t>3,8 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23" t="inlineStr">
-        <is>
-          <t>22,9P x 37l x 35,6H centimètres</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23" t="inlineStr">
-        <is>
-          <t>4.66 kg</t>
-        </is>
-      </c>
-      <c r="BO36" s="23" t="inlineStr">
-        <is>
-          <t>4.66 kg</t>
-        </is>
-      </c>
-      <c r="BP36" s="23" t="inlineStr">
-        <is>
-          <t>45.1 x 36.6 x 20.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ36" s="23" t="inlineStr">
-        <is>
-          <t>45.10 x 36.60 x 20.50 cm</t>
-        </is>
-      </c>
-      <c r="BR36" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>36</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>B01HZUX61M</t>
-        </is>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Marque: Tech'N'Fast | Forme de l'article: Liquide | Parfum: Lavande | Usages spécifiques pour le produit: Moquette | Caractéristique du matériau: Biodégradable | Nombre d'unités: 5000.00 millilitre</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Tech'N'Fast</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - Bidon 5L- pulvérisateur 600 ml offert</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>Nettoyage multi-textiles – Canapés, moquettes, tapis, sièges auto, fauteuils, rideaux, matelas et tissus d’ameublement.
 Efficacité immédiate – Dissout rapidement taches de café, vin, graisse, nourriture, transpiration ou traces d’animaux.
@@ -17178,19 +16830,250 @@
 Format économique 5 L – Idéal pour les grands ménages, hôtels, bureaux, ou nettoyage professionnel.</t>
         </is>
       </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>B01HZUX61M</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O36" s="15">
+        <v>19149</v>
+      </c>
+      <c r="P36" s="15">
+        <v>2406</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>0.21</v>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="S36" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T36" s="15">
+        <v>211</v>
+      </c>
+      <c r="U36" s="16">
+        <v>1.9</v>
+      </c>
+      <c r="V36" s="15">
+        <v>5992</v>
+      </c>
+      <c r="W36" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X36" s="15">
+        <v>3416</v>
+      </c>
+      <c r="Y36" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="20">
+        <v>28.4</v>
+      </c>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="19">
+        <v>50</v>
+      </c>
+      <c r="AE36" s="15">
+        <v>7</v>
+      </c>
+      <c r="AF36" s="21">
+        <v>4.2</v>
+      </c>
+      <c r="AG36" s="22">
+        <v>0.0332</v>
+      </c>
+      <c r="AH36" s="20">
+        <v>11.12</v>
+      </c>
+      <c r="AI36" s="16">
+        <v>0.46</v>
+      </c>
+      <c r="AJ36"/>
+      <c r="AK36" s="13" t="inlineStr">
+        <is>
+          <t>2017-12-18</t>
+        </is>
+      </c>
+      <c r="AL36" s="19">
+        <v>3205</v>
+      </c>
+      <c r="AM36" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN36" s="13"/>
+      <c r="AO36" s="13"/>
+      <c r="AP36" s="20"/>
+      <c r="AQ36" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR36" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS36" s="14" t="inlineStr">
+        <is>
+          <t>DistriPro</t>
+        </is>
+      </c>
+      <c r="AT36" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU36" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV36" s="14" t="inlineStr">
+        <is>
+          <t>Grisy Suisnes 77166 FR</t>
+        </is>
+      </c>
+      <c r="AW36" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+        </is>
+      </c>
+      <c r="AX36" s="13"/>
+      <c r="AY36" s="13"/>
+      <c r="AZ36" s="13"/>
+      <c r="BA36" s="13"/>
+      <c r="BB36" s="13"/>
+      <c r="BC36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE36" s="13"/>
+      <c r="BF36" s="13"/>
+      <c r="BG36" s="13"/>
+      <c r="BH36" s="14"/>
+      <c r="BI36" s="23"/>
+      <c r="BJ36" s="23" t="inlineStr">
+        <is>
+          <t>200 grammes</t>
+        </is>
+      </c>
+      <c r="BK36" s="23" t="inlineStr">
+        <is>
+          <t>200.00 g</t>
+        </is>
+      </c>
+      <c r="BL36" s="23" t="inlineStr">
+        <is>
+          <t>18 x 14 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="23" t="inlineStr">
+        <is>
+          <t>18.00 x 14.00 x 25.00 cm</t>
+        </is>
+      </c>
+      <c r="BN36" s="23" t="inlineStr">
+        <is>
+          <t>200 g</t>
+        </is>
+      </c>
+      <c r="BO36" s="23" t="inlineStr">
+        <is>
+          <t>200.00 g</t>
+        </is>
+      </c>
+      <c r="BP36" s="23"/>
+      <c r="BQ36" s="23"/>
+      <c r="BR36" s="13"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
+        <v>36</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>B0H3B6H4TM</t>
+        </is>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Marque: dreame | Caractéristique spéciale: Arrêt automatique | Recommandation de surface: Tapis | Nom de modèle: N20 Steam | Facteur de forme: Portatif | Couleur: Black | Température maximale: 100 Degrés Celsius | Point fort de l’article: aspir. 17 000Pa, lavage à 70 °C, nett. tissus/tapis/moquettes, outils polyvalents, mélange solution auto., nett. tuyau auto. | Nombre d'articles: 1</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>dreame</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=dreame</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>DREAME N20 Steam Nettoyeur précision portable pr tapis, vapeur 100 °C</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Nettoyage à la vapeur en profondeur à 100 °C: La vapeur haute température pénètre en profondeur dans les tissus pour faire disparaître les taches légères et éliminer 99,9 % des bactéries et &gt; 99 % des acariens. Contrairement au nettoyage traditionnel, la vapeur puissante pénètre à l'intérieur des fibres, rafraîchissant les vêtements et les textiles pour un nettoyage hygiénique en profondeur.
+Élimination des taches tenaces à l'eau chaude à 70 °C: L'eau chaude décompose la graisse, les huiles et les saletés incrustées plus efficacement que l'eau froide. Elle pénètre en profondeur dans les fibres textiles pour un nettoyage supérieur et une fraîcheur durable sur différentes surfaces.
+L'aspiration de 17 000 Pa permet d'éliminer la saleté en quelques secondes: Des taches tenaces ? Aucun problème. Le N20 Steam permet une extraction puissante et efficace de la saleté, de l'humidité et des débris des tissus d’ameublement, tapis et moquettes,, éliminant ainsi les résidus profondément incrustés et laissant les tissus visiblement plus propres et plus hygiéniques.
+Accessoires polyvalents pour surfaces dures: Le N20 Steam propose des accessoires polyvalents qui étendent la puissance de nettoyage au-delà des tissus, permettant une élimination précise de la saleté dans les cuisines, sur le carrelage et dans les coins étroits pour un nettoyage ciblé et en profondeur dans toute la maison.
+Mélange automatique intelligent et protection contre les débordements: Protection anti-débordement intelligente : le capteur intégré arrête l'aspiration lorsque le réservoir d'eau sale est presque plein, permettant d'éviter les débordements. Il dose automatiquement la quantité optimale de solution de nettoyage, ce qui réduit le nombre de remplissages et garantit des résultats homogènes.
+Nettoyage automatique du tuyau en une pression: Vous détestez frotter les tuyaux après le nettoyage ? Le N20 Steam vous facilite la tâche grâce à l'outil de nettoyage automatique et à une aspiration puissante qui éliminent la saleté et les odeurs cachées, tout en gardant votre tuyau propre sans effort supplémentaire.</t>
+        </is>
+      </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H3B6H4TM?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31rbfP6p0aL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B0H3B6H4TM</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -17204,13 +17087,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>19149</v>
+        <v>24973</v>
       </c>
       <c r="P37" s="15">
-        <v>2406</v>
+        <v>14596</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -17219,101 +17102,85 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>211</v>
-      </c>
-      <c r="U37" s="16">
-        <v>1.9</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="U37" s="16"/>
       <c r="V37" s="15">
-        <v>5992</v>
-      </c>
-      <c r="W37" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X37" s="15">
-        <v>3416</v>
-      </c>
+        <v>5960</v>
+      </c>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
       <c r="Y37" s="19">
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>28.4</v>
+        <v>124.17</v>
       </c>
       <c r="AA37" s="4"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>50</v>
-      </c>
-      <c r="AE37" s="15">
-        <v>7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE37" s="15"/>
       <c r="AF37" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.0332</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>11.12</v>
+        <v>11.25</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2017-12-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>3205</v>
+        <v>83</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN37" s="13"/>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AN37" s="13" t="inlineStr">
+        <is>
+          <t>16天</t>
+        </is>
+      </c>
       <c r="AO37" s="13"/>
-      <c r="AP37" s="20"/>
+      <c r="AP37" s="20">
+        <v>147.24</v>
+      </c>
       <c r="AQ37" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR37" s="19">
         <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>DistriPro</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>Grisy Suisnes 77166 FR</t>
-        </is>
-      </c>
-      <c r="AW37" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU37" s="13"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="13"/>
       <c r="AX37" s="13"/>
       <c r="AY37" s="13"/>
       <c r="AZ37" s="13"/>
@@ -17324,49 +17191,61 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
+      <c r="BD37" s="13"/>
+      <c r="BE37" s="13"/>
+      <c r="BF37" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE37" s="13"/>
-      <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
       <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>200 grammes</t>
+          <t>14,8 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
+          <t>14.80 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>18 x 14 x 25 cm</t>
+          <t>44 x 19.5 x 34.5 cm</t>
         </is>
       </c>
       <c r="BM37" s="23" t="inlineStr">
         <is>
-          <t>18.00 x 14.00 x 25.00 cm</t>
+          <t>44.00 x 19.50 x 34.50 cm</t>
         </is>
       </c>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>21 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
-        </is>
-      </c>
-      <c r="BP37" s="23"/>
-      <c r="BQ37" s="23"/>
-      <c r="BR37" s="13"/>
+          <t>21.00 kg</t>
+        </is>
+      </c>
+      <c r="BP37" s="23" t="inlineStr">
+        <is>
+          <t>60 x 44.5 x 36 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="23" t="inlineStr">
+        <is>
+          <t>60.00 x 44.50 x 36.00 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="13" t="inlineStr">
+        <is>
+          <t>重型标准大件</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
@@ -17375,258 +17254,31 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0H3B6H4TM</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Marque: dreame | Caractéristique spéciale: Arrêt automatique | Recommandation de surface: Tapis | Nom de modèle: N20 Steam | Facteur de forme: Portatif | Couleur: Black | Température maximale: 100 Degrés Celsius | Point fort de l’article: aspir. 17 000Pa, lavage à 70 °C, nett. tissus/tapis/moquettes, outils polyvalents, mélange solution auto., nett. tuyau auto. | Nombre d'articles: 1</t>
+          <t>Marque: Hearten | Couleur: Blanc | Poids de l'article: 2,5 Kilogrammes | Dimensions du produit: 23,2P x 29,9l x 17,3H centimètres | Capacité: 1,5 litres | Nombre d'unités: 1 Compteur | Fabricant: Hearten | Nombre d'articles: 1 | Point fort de l’article: Nettoyeur Canapé Tissu, Compact et Portable, 1.5L Réservoir, Accessoires Variés, pour Canapé, Tapis, Rembourrage, Voiture</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=dreame</t>
+          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>DREAME N20 Steam Nettoyeur précision portable pr tapis, vapeur 100 °C</t>
+          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec Autonettoyant</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Nettoyage à la vapeur en profondeur à 100 °C: La vapeur haute température pénètre en profondeur dans les tissus pour faire disparaître les taches légères et éliminer 99,9 % des bactéries et &gt; 99 % des acariens. Contrairement au nettoyage traditionnel, la vapeur puissante pénètre à l'intérieur des fibres, rafraîchissant les vêtements et les textiles pour un nettoyage hygiénique en profondeur.
-Élimination des taches tenaces à l'eau chaude à 70 °C: L'eau chaude décompose la graisse, les huiles et les saletés incrustées plus efficacement que l'eau froide. Elle pénètre en profondeur dans les fibres textiles pour un nettoyage supérieur et une fraîcheur durable sur différentes surfaces.
-L'aspiration de 17 000 Pa permet d'éliminer la saleté en quelques secondes: Des taches tenaces ? Aucun problème. Le N20 Steam permet une extraction puissante et efficace de la saleté, de l'humidité et des débris des tissus d’ameublement, tapis et moquettes,, éliminant ainsi les résidus profondément incrustés et laissant les tissus visiblement plus propres et plus hygiéniques.
-Accessoires polyvalents pour surfaces dures: Le N20 Steam propose des accessoires polyvalents qui étendent la puissance de nettoyage au-delà des tissus, permettant une élimination précise de la saleté dans les cuisines, sur le carrelage et dans les coins étroits pour un nettoyage ciblé et en profondeur dans toute la maison.
-Mélange automatique intelligent et protection contre les débordements: Protection anti-débordement intelligente : le capteur intégré arrête l'aspiration lorsque le réservoir d'eau sale est presque plein, permettant d'éviter les débordements. Il dose automatiquement la quantité optimale de solution de nettoyage, ce qui réduit le nombre de remplissages et garantit des résultats homogènes.
-Nettoyage automatique du tuyau en une pression: Vous détestez frotter les tuyaux après le nettoyage ? Le N20 Steam vous facilite la tâche grâce à l'outil de nettoyage automatique et à une aspiration puissante qui éliminent la saleté et les odeurs cachées, tout en gardant votre tuyau propre sans effort supplémentaire.</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0H3B6H4TM?psc=1</t>
-        </is>
-      </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31rbfP6p0aL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L38" s="14" t="inlineStr">
-        <is>
-          <t>B0H3B6H4TM</t>
-        </is>
-      </c>
-      <c r="M38" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O38" s="15">
-        <v>24973</v>
-      </c>
-      <c r="P38" s="15">
-        <v>14596</v>
-      </c>
-      <c r="Q38" s="16">
-        <v>0.38</v>
-      </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S38" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="T38" s="15">
-        <v>40</v>
-      </c>
-      <c r="U38" s="16"/>
-      <c r="V38" s="15">
-        <v>5960</v>
-      </c>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>124.17</v>
-      </c>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="20">
-        <v>11.25</v>
-      </c>
-      <c r="AI38" s="16">
-        <v>0.77</v>
-      </c>
-      <c r="AJ38"/>
-      <c r="AK38" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="AL38" s="19">
-        <v>83</v>
-      </c>
-      <c r="AM38" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN38" s="13" t="inlineStr">
-        <is>
-          <t>16天</t>
-        </is>
-      </c>
-      <c r="AO38" s="13"/>
-      <c r="AP38" s="20">
-        <v>147.24</v>
-      </c>
-      <c r="AQ38" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR38" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS38" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT38" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="13"/>
-      <c r="AX38" s="13"/>
-      <c r="AY38" s="13"/>
-      <c r="AZ38" s="13"/>
-      <c r="BA38" s="13"/>
-      <c r="BB38" s="13"/>
-      <c r="BC38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD38" s="13"/>
-      <c r="BE38" s="13"/>
-      <c r="BF38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG38" s="13"/>
-      <c r="BH38" s="14"/>
-      <c r="BI38" s="23"/>
-      <c r="BJ38" s="23" t="inlineStr">
-        <is>
-          <t>14,8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK38" s="23" t="inlineStr">
-        <is>
-          <t>14.80 kg</t>
-        </is>
-      </c>
-      <c r="BL38" s="23" t="inlineStr">
-        <is>
-          <t>44 x 19.5 x 34.5 cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="23" t="inlineStr">
-        <is>
-          <t>44.00 x 19.50 x 34.50 cm</t>
-        </is>
-      </c>
-      <c r="BN38" s="23" t="inlineStr">
-        <is>
-          <t>21 kg</t>
-        </is>
-      </c>
-      <c r="BO38" s="23" t="inlineStr">
-        <is>
-          <t>21.00 kg</t>
-        </is>
-      </c>
-      <c r="BP38" s="23" t="inlineStr">
-        <is>
-          <t>60 x 44.5 x 36 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="23" t="inlineStr">
-        <is>
-          <t>60.00 x 44.50 x 36.00 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="13" t="inlineStr">
-        <is>
-          <t>重型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
-        <v>38</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>B0H263J8GJ</t>
-        </is>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Marque: Hearten | Couleur: Blanc | Poids de l'article: 2,5 Kilogrammes | Dimensions du produit: 23,2P x 29,9l x 17,3H centimètres | Capacité: 1,5 litres | Nombre d'unités: 1 Compteur | Fabricant: Hearten | Nombre d'articles: 1 | Point fort de l’article: Nettoyeur Canapé Tissu, Compact et Portable, 1.5L Réservoir, Accessoires Variés, pour Canapé, Tapis, Rembourrage, Voiture</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>Hearten</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec Autonettoyant</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>【Aspiration puissante】Cette shampouineuse canapé est équipée d'un moteur haute performance, offrant une aspiration puissante de 22 kPa qui pénètre profondément dans les fibres des tissus, éliminant facilement la poussière tenace et les taches sur les tapis, canapés, matelas et sièges auto. Qu'il s'agisse de liquides renversés, de boissons ou de taches d'urine d'animaux, tout est aspiré en un seul passage, sans laisser de traces.
 【Auto-nettoyage】Ce nettoyeur tapis est doté d'une fonction d'auto-nettoyage. Après le nettoyage, il suffit de remplacer la brosse par l'embout de nettoyage, de maintenir le bouton enfoncé et le tuyau intérieur se nettoie automatiquement, évitant les résidus de saleté et les mauvaises odeurs. Sans démontage ni lavage manuel, l'entretien quotidien est simple et rapide, et l'appareil reste toujours propre.
@@ -17635,246 +17287,246 @@
 【Rangement pratique】Notre aspirateur canapé est livré avec deux brosses : une brosse standard pour le nettoyage quotidien et une brosse spéciale poils d'animaux pour éliminer facilement les poils. Il est également équipé d'un support de poignée et d'un clip de rangement pour le câble, permettant un rangement ordonné et gain de place, tout en évitant les enchevêtrements.</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="L38" s="14" t="inlineStr">
         <is>
           <t>B0H263J8GJ</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr">
+      <c r="M38" s="14" t="inlineStr">
         <is>
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="N39" s="14" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
-      <c r="O39" s="15">
+      <c r="O38" s="15">
         <v>19730</v>
       </c>
-      <c r="P39" s="15">
+      <c r="P38" s="15">
         <v>17275</v>
       </c>
-      <c r="Q39" s="16">
+      <c r="Q38" s="16">
         <v>0.61</v>
       </c>
-      <c r="R39" s="17" t="inlineStr">
+      <c r="R38" s="17" t="inlineStr">
         <is>
           <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="S39" s="18" t="inlineStr">
+      <c r="S38" s="18" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T39" s="15">
+      <c r="T38" s="15">
         <v>85</v>
       </c>
-      <c r="U39" s="16"/>
-      <c r="V39" s="15">
+      <c r="U38" s="16"/>
+      <c r="V38" s="15">
         <v>5609</v>
       </c>
-      <c r="W39" s="15" t="inlineStr">
+      <c r="W38" s="15" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="X39" s="15">
+      <c r="X38" s="15">
         <v>3735</v>
       </c>
-      <c r="Y39" s="19">
+      <c r="Y38" s="19">
         <v>1</v>
       </c>
-      <c r="Z39" s="20">
+      <c r="Z38" s="20">
         <v>65.99</v>
       </c>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="2"/>
-      <c r="AD39" s="19">
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="19">
         <v>21</v>
       </c>
-      <c r="AE39" s="15">
+      <c r="AE38" s="15">
         <v>13</v>
       </c>
-      <c r="AF39" s="21">
+      <c r="AF38" s="21">
         <v>4.2</v>
       </c>
-      <c r="AG39" s="22">
+      <c r="AG38" s="22">
         <v>0.15289999999999998</v>
       </c>
-      <c r="AH39" s="20">
+      <c r="AH38" s="20">
         <v>8.11</v>
       </c>
-      <c r="AI39" s="16">
+      <c r="AI38" s="16">
         <v>0.73</v>
       </c>
-      <c r="AJ39"/>
-      <c r="AK39" s="13" t="inlineStr">
+      <c r="AJ38"/>
+      <c r="AK38" s="13" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AL39" s="19">
+      <c r="AL38" s="19">
         <v>35</v>
       </c>
-      <c r="AM39" s="13" t="inlineStr">
+      <c r="AM38" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39" s="20"/>
-      <c r="AQ39" s="19">
+      <c r="AN38" s="13"/>
+      <c r="AO38" s="13"/>
+      <c r="AP38" s="20"/>
+      <c r="AQ38" s="19">
         <v>10</v>
       </c>
-      <c r="AR39" s="19">
+      <c r="AR38" s="19">
         <v>1</v>
       </c>
-      <c r="AS39" s="14" t="inlineStr">
+      <c r="AS38" s="14" t="inlineStr">
         <is>
           <t>Hearten Direct</t>
         </is>
       </c>
-      <c r="AT39" s="13" t="inlineStr">
+      <c r="AT38" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU39" s="13" t="inlineStr">
+      <c r="AU38" s="13" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV39" s="14" t="inlineStr">
+      <c r="AV38" s="14" t="inlineStr">
         <is>
           <t>Hong Kong 999077 HK</t>
         </is>
       </c>
-      <c r="AW39" s="13" t="inlineStr">
+      <c r="AW38" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
         </is>
       </c>
-      <c r="AX39" s="13"/>
-      <c r="AY39" s="13" t="inlineStr">
+      <c r="AX38" s="13"/>
+      <c r="AY38" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ39" s="13"/>
-      <c r="BA39" s="13"/>
-      <c r="BB39" s="13"/>
-      <c r="BC39" s="13" t="inlineStr">
+      <c r="AZ38" s="13"/>
+      <c r="BA38" s="13"/>
+      <c r="BB38" s="13"/>
+      <c r="BC38" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD39" s="13" t="inlineStr">
+      <c r="BD38" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE39" s="13"/>
-      <c r="BF39" s="13" t="inlineStr">
+      <c r="BE38" s="13"/>
+      <c r="BF38" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG39" s="13"/>
-      <c r="BH39" s="14"/>
-      <c r="BI39" s="23" t="inlineStr">
+      <c r="BG38" s="13"/>
+      <c r="BH38" s="14"/>
+      <c r="BI38" s="23" t="inlineStr">
         <is>
           <t>Choix d'Amazon</t>
         </is>
       </c>
-      <c r="BJ39" s="23" t="inlineStr">
+      <c r="BJ38" s="23" t="inlineStr">
         <is>
           <t>2,5 Kilogrammes</t>
         </is>
       </c>
-      <c r="BK39" s="23"/>
-      <c r="BL39" s="23" t="inlineStr">
+      <c r="BK38" s="23"/>
+      <c r="BL38" s="23" t="inlineStr">
         <is>
           <t>23,2P x 29,9l x 17,3H centimètres</t>
         </is>
       </c>
-      <c r="BM39" s="23"/>
-      <c r="BN39" s="23" t="inlineStr">
+      <c r="BM38" s="23"/>
+      <c r="BN38" s="23" t="inlineStr">
         <is>
           <t>3.34 kg</t>
         </is>
       </c>
-      <c r="BO39" s="23" t="inlineStr">
+      <c r="BO38" s="23" t="inlineStr">
         <is>
           <t>3.34 kg</t>
         </is>
       </c>
-      <c r="BP39" s="23" t="inlineStr">
+      <c r="BP38" s="23" t="inlineStr">
         <is>
           <t>32.4 x 32.2 x 19.4 cm</t>
         </is>
       </c>
-      <c r="BQ39" s="23" t="inlineStr">
+      <c r="BQ38" s="23" t="inlineStr">
         <is>
           <t>32.40 x 32.20 x 19.40 cm</t>
         </is>
       </c>
-      <c r="BR39" s="13" t="inlineStr">
+      <c r="BR38" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13">
-        <v>39</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14" t="inlineStr">
+    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
+        <v>38</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>B0HHNM96WW</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Couleur: Gris</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Marque: Lubluelu | Couleur: Gris | Poids de l'article: 3 Kilogrammes | Dimensions du produit: 15,2P x 35l x 32H centimètres | Capacité: 2,75 litres | Source d'alimentation: Câble électrique | Nombre d’emballages: 1 | Nombre d'unités: 1 Compteur | Fabricant: Lubluelu | Nombre d'articles: 1</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Lubluelu</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>Lubluelu Shampouineuse Canapé 22 kPa, 600 W, Nettoyeur Tapis Portable</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>【Nettoyage en profondeur 600 W &amp; 22 kPa】Équipée d’un moteur haute performance de 600 W, cette shampouineuse développe une puissance d’aspiration jusqu’à 22 kPa. Elle élimine efficacement la poussière incrustée, les saletés et les taches tenaces telles que le lait, le café ou l’urine sur les tapis et les canapés.
 【Double réservoirs 1,75 L】Cet injecteur extracteur dispose de deux réservoirs séparés pour l’eau propre et l’eau sale, offrant une plus grande autonomie. Une seule recharge permet de nettoyer env. 4 m² de tapis tout en réduisant les changements d’eau.
@@ -17884,234 +17536,234 @@
 【Service client de qualité】Pour toute question concernant votre nettoyeur canapé Lubluelu, veuillez nous contacter via l’e-mail du service client. Notre équipe professionnelle est à votre écoute pour vous offrir une assistance rapide et une entière satisfaction.</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/dp/B0HHNM96WW?psc=1</t>
         </is>
       </c>
-      <c r="K40" s="14" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="L39" s="14" t="inlineStr">
         <is>
           <t>B0HJR5CK76</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="M39" s="14" t="inlineStr">
         <is>
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="N40" s="14" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
-      <c r="O40" s="15">
+      <c r="O39" s="15">
         <v>1509</v>
       </c>
-      <c r="P40" s="15">
+      <c r="P39" s="15">
         <v>27851</v>
       </c>
-      <c r="Q40" s="16">
+      <c r="Q39" s="16">
         <v>0.89</v>
       </c>
-      <c r="R40" s="17" t="inlineStr">
+      <c r="R39" s="17" t="inlineStr">
         <is>
           <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="S40" s="18" t="inlineStr">
+      <c r="S39" s="18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T40" s="15">
+      <c r="T39" s="15">
         <v>66</v>
       </c>
-      <c r="U40" s="16"/>
-      <c r="V40" s="15">
+      <c r="U39" s="16"/>
+      <c r="V39" s="15">
         <v>5279</v>
       </c>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="19">
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="19">
         <v>1</v>
       </c>
-      <c r="Z40" s="20">
+      <c r="Z39" s="20">
         <v>66.66</v>
       </c>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="19">
         <v>17</v>
       </c>
-      <c r="AE40" s="15">
+      <c r="AE39" s="15">
         <v>0</v>
       </c>
-      <c r="AF40" s="21">
+      <c r="AF39" s="21">
         <v>5</v>
       </c>
-      <c r="AG40" s="22">
+      <c r="AG39" s="22">
         <v>0</v>
       </c>
-      <c r="AH40" s="20">
+      <c r="AH39" s="20">
         <v>8.97</v>
       </c>
-      <c r="AI40" s="16">
+      <c r="AI39" s="16">
         <v>0.74</v>
       </c>
-      <c r="AJ40"/>
-      <c r="AK40" s="13" t="inlineStr">
+      <c r="AJ39"/>
+      <c r="AK39" s="13" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AL40" s="19">
+      <c r="AL39" s="19">
         <v>20</v>
       </c>
-      <c r="AM40" s="13" t="inlineStr">
+      <c r="AM39" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AN40" s="13" t="inlineStr">
+      <c r="AN39" s="13" t="inlineStr">
         <is>
           <t>16天</t>
         </is>
       </c>
-      <c r="AO40" s="13"/>
-      <c r="AP40" s="20">
+      <c r="AO39" s="13"/>
+      <c r="AP39" s="20">
         <v>56.76</v>
       </c>
-      <c r="AQ40" s="19">
+      <c r="AQ39" s="19">
         <v>10</v>
       </c>
-      <c r="AR40" s="19">
+      <c r="AR39" s="19">
         <v>1</v>
       </c>
-      <c r="AS40" s="14" t="inlineStr">
+      <c r="AS39" s="14" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT40" s="13" t="inlineStr">
+      <c r="AT39" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AU40" s="13"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="13"/>
-      <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
+      <c r="AU39" s="13"/>
+      <c r="AV39" s="14"/>
+      <c r="AW39" s="13"/>
+      <c r="AX39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="13"/>
-      <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
+      <c r="AZ39" s="13"/>
+      <c r="BA39" s="13"/>
+      <c r="BB39" s="13"/>
+      <c r="BC39" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD40" s="13" t="inlineStr">
+      <c r="BD39" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE40" s="13"/>
-      <c r="BF40" s="13" t="inlineStr">
+      <c r="BE39" s="13"/>
+      <c r="BF39" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG40" s="13"/>
-      <c r="BH40" s="14" t="inlineStr">
+      <c r="BG39" s="13"/>
+      <c r="BH39" s="14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BI40" s="23" t="inlineStr">
+      <c r="BI39" s="23" t="inlineStr">
         <is>
           <t>Choix d'Amazon</t>
         </is>
       </c>
-      <c r="BJ40" s="23" t="inlineStr">
+      <c r="BJ39" s="23" t="inlineStr">
         <is>
           <t>3 Kilogrammes</t>
         </is>
       </c>
-      <c r="BK40" s="23"/>
-      <c r="BL40" s="23" t="inlineStr">
+      <c r="BK39" s="23"/>
+      <c r="BL39" s="23" t="inlineStr">
         <is>
           <t>15,2P x 35l x 32H centimètres</t>
         </is>
       </c>
-      <c r="BM40" s="23"/>
-      <c r="BN40" s="23" t="inlineStr">
+      <c r="BM39" s="23"/>
+      <c r="BN39" s="23" t="inlineStr">
         <is>
           <t>4.13 kg</t>
         </is>
       </c>
-      <c r="BO40" s="23" t="inlineStr">
+      <c r="BO39" s="23" t="inlineStr">
         <is>
           <t>4.13 kg</t>
         </is>
       </c>
-      <c r="BP40" s="23" t="inlineStr">
+      <c r="BP39" s="23" t="inlineStr">
         <is>
           <t>44.2 x 33.9 x 20 cm</t>
         </is>
       </c>
-      <c r="BQ40" s="23" t="inlineStr">
+      <c r="BQ39" s="23" t="inlineStr">
         <is>
           <t>44.20 x 33.90 x 20.00 cm</t>
         </is>
       </c>
-      <c r="BR40" s="13" t="inlineStr">
+      <c r="BR39" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
-        <v>40</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14" t="inlineStr">
+    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13">
+        <v>39</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>B0H3LCDNGF</t>
         </is>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Marque: LEHMANN | Couleur: Noir/Rouge | Poids de l'article: 4,7 Kilogrammes | Dimensions du produit: 22P x 32l x 30H centimètres | Style: Contemporain | Nom de modèle: SteamWash | Capacité: 1,9 litres | Source d'alimentation: Câble électrique | Nombre d'unités: 1.0 unité | Fabricant: LEHMANN</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>LEHMANN</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis, Voiture, Eau Chaude 60°C, Vapeur 116°C, 16 kPa</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>4 modes de nettoyage dans un seul appareil : eau froide, eau chaude, vapeur textile et vapeur haute température : Lehmann SteamWash réunit les fonctions d'une shampouineuse canapé, d'une shampouineuse tapis, d'un nettoyeur tapis et moquettes et d'un nettoyeur vapeur portable dans un seul appareil compact. Choisissez entre le lavage à l'eau froide, le lavage à l'eau chaude (env. 60°C), le nettoyage des textiles à la vapeur ou la vapeur haute température (env. 116°C) pour les joints, carrelages, vitres et autres surfaces. Une solution polyvalente pour nettoyer canapés, tapis, moquettes, sièges de voiture, matelas et toute la maison
 Nettoyage en profondeur des tissus, tapis, moquettes et intérieurs de voiture: Grâce à son système de pulvérisation et à sa puissance d’aspiration ≥16 kPa, SteamWash aide à éliminer les taches, la saleté incrustée et les résidus responsables des mauvaises odeurs. Utilisé comme shampouineuse canapé ou shampouineuse tapis, il permet de nettoyer efficacement les textiles du quotidien, notamment dans les foyers avec enfants ou animaux de compagnie. Une solution pratique pour entretenir canapés, moquettes, tapis et sièges automobiles sans avoir recours à plusieurs appareils
@@ -18120,226 +17772,226 @@
 Confort d’utilisation et entretien simplifié: Réservoir d’eau propre de 1,9 L, réservoir d’eau sale de 1,4 L, flexible de 2,3 m, câble de 4 m et roulettes 360° pour une excellente maniabilité. La fonction d’auto-nettoyage facilite l’entretien du système après utilisation</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41Md9nniqDL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L41" s="14" t="inlineStr">
+      <c r="L40" s="14" t="inlineStr">
         <is>
           <t>B0H3LCDNGF</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr">
+      <c r="M40" s="14" t="inlineStr">
         <is>
           <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="N41" s="14" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
-      <c r="O41" s="15">
+      <c r="O40" s="15">
         <v>28155</v>
       </c>
-      <c r="P41" s="15">
+      <c r="P40" s="15">
         <v>20364</v>
       </c>
-      <c r="Q41" s="16">
+      <c r="Q40" s="16">
         <v>0.36</v>
       </c>
-      <c r="R41" s="17" t="inlineStr">
+      <c r="R40" s="17" t="inlineStr">
         <is>
           <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
-      <c r="S41" s="18" t="inlineStr">
+      <c r="S40" s="18" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="T41" s="15">
+      <c r="T40" s="15">
         <v>52</v>
       </c>
-      <c r="U41" s="16">
+      <c r="U40" s="16">
         <v>7.18</v>
       </c>
-      <c r="V41" s="15">
+      <c r="V40" s="15">
         <v>5199</v>
       </c>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="19">
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="19">
         <v>1</v>
       </c>
-      <c r="Z41" s="20">
+      <c r="Z40" s="20">
         <v>99.99</v>
       </c>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="2"/>
-      <c r="AD41" s="19">
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="19">
         <v>37</v>
       </c>
-      <c r="AE41" s="15">
+      <c r="AE40" s="15">
         <v>14</v>
       </c>
-      <c r="AF41" s="21">
+      <c r="AF40" s="21">
         <v>4</v>
       </c>
-      <c r="AG41" s="22">
+      <c r="AG40" s="22">
         <v>0.2692</v>
       </c>
-      <c r="AH41" s="20">
+      <c r="AH40" s="20">
         <v>9.1</v>
       </c>
-      <c r="AI41" s="16">
+      <c r="AI40" s="16">
         <v>0.76</v>
       </c>
-      <c r="AJ41"/>
-      <c r="AK41" s="13" t="inlineStr">
+      <c r="AJ40"/>
+      <c r="AK40" s="13" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AL41" s="19">
+      <c r="AL40" s="19">
         <v>118</v>
       </c>
-      <c r="AM41" s="13" t="inlineStr">
+      <c r="AM40" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN41" s="13"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41" s="20"/>
-      <c r="AQ41" s="19">
+      <c r="AN40" s="13"/>
+      <c r="AO40" s="13"/>
+      <c r="AP40" s="20"/>
+      <c r="AQ40" s="19">
         <v>10</v>
       </c>
-      <c r="AR41" s="19">
+      <c r="AR40" s="19">
         <v>1</v>
       </c>
-      <c r="AS41" s="14" t="inlineStr">
+      <c r="AS40" s="14" t="inlineStr">
         <is>
           <t>Lehmann HG</t>
         </is>
       </c>
-      <c r="AT41" s="13" t="inlineStr">
+      <c r="AT40" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU41" s="13" t="inlineStr">
+      <c r="AU40" s="13" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="AV41" s="14" t="inlineStr">
+      <c r="AV40" s="14" t="inlineStr">
         <is>
           <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
-      <c r="AW41" s="13" t="inlineStr">
+      <c r="AW40" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
-      <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
-      <c r="AZ41" s="13"/>
-      <c r="BA41" s="13"/>
-      <c r="BB41" s="13"/>
-      <c r="BC41" s="13" t="inlineStr">
+      <c r="AX40" s="13"/>
+      <c r="AY40" s="13"/>
+      <c r="AZ40" s="13"/>
+      <c r="BA40" s="13"/>
+      <c r="BB40" s="13"/>
+      <c r="BC40" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13"/>
-      <c r="BE41" s="13"/>
-      <c r="BF41" s="13" t="inlineStr">
+      <c r="BD40" s="13"/>
+      <c r="BE40" s="13"/>
+      <c r="BF40" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG41" s="13"/>
-      <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
-      <c r="BJ41" s="23" t="inlineStr">
+      <c r="BG40" s="13"/>
+      <c r="BH40" s="14"/>
+      <c r="BI40" s="23"/>
+      <c r="BJ40" s="23" t="inlineStr">
         <is>
           <t>4,7 Kilogrammes</t>
         </is>
       </c>
-      <c r="BK41" s="23"/>
-      <c r="BL41" s="23" t="inlineStr">
+      <c r="BK40" s="23"/>
+      <c r="BL40" s="23" t="inlineStr">
         <is>
           <t>22P x 32l x 30H centimètres</t>
         </is>
       </c>
-      <c r="BM41" s="23"/>
-      <c r="BN41" s="23" t="inlineStr">
+      <c r="BM40" s="23"/>
+      <c r="BN40" s="23" t="inlineStr">
         <is>
           <t>5.76 kg</t>
         </is>
       </c>
-      <c r="BO41" s="23" t="inlineStr">
+      <c r="BO40" s="23" t="inlineStr">
         <is>
           <t>5.76 kg</t>
         </is>
       </c>
-      <c r="BP41" s="23" t="inlineStr">
+      <c r="BP40" s="23" t="inlineStr">
         <is>
           <t>37.3 x 35.7 x 31.8 cm</t>
         </is>
       </c>
-      <c r="BQ41" s="23" t="inlineStr">
+      <c r="BQ40" s="23" t="inlineStr">
         <is>
           <t>37.30 x 35.70 x 31.80 cm</t>
         </is>
       </c>
-      <c r="BR41" s="13" t="inlineStr">
+      <c r="BR40" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
-        <v>41</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14" t="inlineStr">
+    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>B0B3J3Q9RD</t>
         </is>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="D41" s="14"/>
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Marque: HAUSHOF | Couleur: Blanc, Gris, Bleu | Poids de l'article: 3,4 Kilogrammes | Dimensions du produit: 15P x 28,5l x 26,5H centimètres | Style: Contemporaine | Nom de modèle: HAUSHOF Nettoyeur de Tapis 400W | Capacité: 1,1 litres | Source d'alimentation: Câble électrique | Fabricant: Hang Zhou Great Star Industrial Co.,Ltd | UPC: 820909778370</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>HAUSHOF</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double Réservoir</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>[Nettoyage efficace] HAUSHOF nettoyeur de tapis est équipé d'un puissant moteur de 400 W avec un niveau sonore de seulement 85 dB sans faire trop de bruit, et offre des fonctions multifonctionnelle d'arrosage, de brossage et d'aspiration, ce qui permet de nettoyer efficacement les tapis, les canapés, les coussins des animaux de compagnie et les sièges de voiture, et d'améliorer l'efficacité du nettoyage
 [Double réservoir indépendant] Le nettoyeur de canapé a double réservoir d'eau amovible qui est plus pratique pour traiter l'eau propre et les eaux usées. La grande capacité du double réservoir d'eau peut être nettoyée à l'eau propre, tandis que la saleté et la poussière sont stockées dans le réservoir séparé. Capacité du réservoir d'eau propre : 1100 ml, capacité du réservoir d'eau sale : 500 ml
@@ -18351,19 +18003,251 @@
 [Remarque 3] Si la quantité d'eau dans le réservoir d'eaux usées dépasse la ligne MAX, la machine continuera à fonctionner mais n'absorbera plus d'eau. Cette conception est conçue pour empêcher la machine de fuir en raison d'un volume d'eau excessif. Pour garantir le bon fonctionnement de l'appareil, nous vous recommandons de vider le réservoir d'eau usée dès que la quantité d'eau dans le réservoir atteint la ligne MAX. Si de l'eau a pénétré dans la machine, veuillez éteigner la machine et vider l'eau à l'intérieur de la machine, du tuyau et du seau et le nettoyeur reprendra son fonctionnement normal</t>
         </is>
       </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
+          <t>B0B3J3Q9RD</t>
+        </is>
+      </c>
+      <c r="M41" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="N41" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O41" s="15">
+        <v>26489</v>
+      </c>
+      <c r="P41" s="15">
+        <v>28314</v>
+      </c>
+      <c r="Q41" s="16">
+        <v>0.42</v>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t>Nettoyeurs tapis et moquettes</t>
+        </is>
+      </c>
+      <c r="S41" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="T41" s="15">
+        <v>74</v>
+      </c>
+      <c r="U41" s="16">
+        <v>-0.08</v>
+      </c>
+      <c r="V41" s="15">
+        <v>5179</v>
+      </c>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="Y41" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="20">
+        <v>69.99</v>
+      </c>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="19">
+        <v>4824</v>
+      </c>
+      <c r="AE41" s="15">
+        <v>18</v>
+      </c>
+      <c r="AF41" s="21">
+        <v>4.2</v>
+      </c>
+      <c r="AG41" s="22">
+        <v>0.2432</v>
+      </c>
+      <c r="AH41" s="20">
+        <v>8.47</v>
+      </c>
+      <c r="AI41" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="AJ41"/>
+      <c r="AK41" s="13" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AL41" s="19">
+        <v>1258</v>
+      </c>
+      <c r="AM41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN41" s="13"/>
+      <c r="AO41" s="13"/>
+      <c r="AP41" s="20"/>
+      <c r="AQ41" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="AT41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="13"/>
+      <c r="AX41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ41" s="13"/>
+      <c r="BA41" s="13"/>
+      <c r="BB41" s="13"/>
+      <c r="BC41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE41" s="13"/>
+      <c r="BF41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG41" s="13"/>
+      <c r="BH41" s="14"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
+      <c r="BJ41" s="23" t="inlineStr">
+        <is>
+          <t>3,4 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK41" s="23"/>
+      <c r="BL41" s="23" t="inlineStr">
+        <is>
+          <t>15P x 28,5l x 26,5H centimètres</t>
+        </is>
+      </c>
+      <c r="BM41" s="23"/>
+      <c r="BN41" s="23" t="inlineStr">
+        <is>
+          <t>4.85 kg</t>
+        </is>
+      </c>
+      <c r="BO41" s="23" t="inlineStr">
+        <is>
+          <t>4.85 kg</t>
+        </is>
+      </c>
+      <c r="BP41" s="23" t="inlineStr">
+        <is>
+          <t>40.2 x 34.2 x 19.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ41" s="23" t="inlineStr">
+        <is>
+          <t>40.20 x 34.20 x 19.50 cm</t>
+        </is>
+      </c>
+      <c r="BR41" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
+        <v>41</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>B0BSHCQQ4W</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Style: TWT77</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Marque: H.Koenig | Couleur: Blanc et Vert | Poids de l'article: 4 Kilogrammes | Dimensions du produit: 36,5P x 24,5l x 31,8H centimètres | Style: TWT77 | Nom de modèle: TWT77 | Capacité: 1,4 litres | Source d'alimentation: Câble électrique | Disponibilité de pièces détachées dans l’UE: 10 Ans | Nombre d'unités: 1.0 unité</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>H.Koenig</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Inclus, Puissant et Compact, 650W</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>[RESERVOIRS DISTINCTS POUR EAU PROPRE ET EAU SALE] : Doté d'un réservoir à eau propre de 1,4 L et d'un réservoir à eau sale de 1,2 L, cet aspirateur assure une séparation efficace pour des résultats de nettoyage optimisés.
+[DEBIT D'EAU REGLABLE ET RESEVOIR AMOVIBLE] : Avec un débit d'eau réglable à 350 mL/min, cet aspirateur offre un contrôle précis. Les réservoirs d'eau sont amovibles pour un remplissage et un vidage faciles.
+[ACCESSOIRES PRATIQUES ET RANGEMENTS INTEGRES] : Livré avec une brosse amovible et un câble d'alimentation de 3 m, cet aspirateur offre des accessoires pratiques. De plus, le rangement intégré pour les câbles électriques facilite le stockage. Le modèle est compact pour faciliter son rangement dans votre maison.
+[PUISSANCE OPTIMALE ET BROSSE DE RECHANGE INCLUSE] : Avec une puissance de 650 W, cet aspirateur garantit une performance optimale. Une brosse de rechange est également incluse pour une utilisation prolongée.
+[GARANTIE ETENDUE DE 2 ANS] : Bénéficiez d'une garantie étendue de 2 ans, accompagnée d'un atelier SAV en France, offrant ainsi la confiance et la tranquillité d'esprit pour une utilisation prolongée et fiable.</t>
+        </is>
+      </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0DBJ2CJ2J</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -18377,13 +18261,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>26489</v>
+        <v>36271</v>
       </c>
       <c r="P42" s="15">
-        <v>28314</v>
+        <v>93859</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -18392,55 +18276,55 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="U42" s="16">
-        <v>-0.08</v>
+        <v>1.89</v>
       </c>
       <c r="V42" s="15">
-        <v>5179</v>
+        <v>4997</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z42" s="20">
-        <v>69.99</v>
+        <v>64.9</v>
       </c>
       <c r="AA42" s="4"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>4824</v>
+        <v>1073</v>
       </c>
       <c r="AE42" s="15">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AF42" s="21">
         <v>4.2</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2432</v>
+        <v>0.0779</v>
       </c>
       <c r="AH42" s="20">
-        <v>8.47</v>
+        <v>9.53</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>1258</v>
+        <v>1317</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -18454,11 +18338,11 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -18466,9 +18350,21 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>Paris 75001 FR</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
       <c r="AY42" s="13" t="inlineStr">
         <is>
@@ -18503,34 +18399,34 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilogrammes</t>
+          <t>4 Kilogrammes</t>
         </is>
       </c>
       <c r="BK42" s="23"/>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>15P x 28,5l x 26,5H centimètres</t>
+          <t>36,5P x 24,5l x 31,8H centimètres</t>
         </is>
       </c>
       <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -18546,56 +18442,52 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>Style: TWT77</t>
-        </is>
-      </c>
+          <t>B08KXVXC82</t>
+        </is>
+      </c>
+      <c r="D43" s="14"/>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>Marque: H.Koenig | Couleur: Blanc et Vert | Poids de l'article: 4 Kilogrammes | Dimensions du produit: 36,5P x 24,5l x 31,8H centimètres | Style: TWT77 | Nom de modèle: TWT77 | Capacité: 1,4 litres | Source d'alimentation: Câble électrique | Disponibilité de pièces détachées dans l’UE: 10 Ans | Nombre d'unités: 1.0 unité</t>
+          <t>Marque: MEDION | Couleur: Gris | Poids de l'article: 4,5 Kilogrammes | Dimensions du produit: 24P x 31,7l x 35H centimètres | Nom de modèle: MD 100122 | Capacité: 1,08 litres | Nombre d'unités: 1.0 unité | Fabricant: MEDION | Nombre d'articles: 1 | Point fort de l’article: Aspirateur eau pour tissus tapis sièges auto, réservoirs propre et sale, embout fenêtre, MD100122</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>MEDION</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Inclus, Puissant et Compact, 650W</t>
+          <t>MEDION E10 UC Nettoyeur textile injecteur extracteur - 750 W</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>[RESERVOIRS DISTINCTS POUR EAU PROPRE ET EAU SALE] : Doté d'un réservoir à eau propre de 1,4 L et d'un réservoir à eau sale de 1,2 L, cet aspirateur assure une séparation efficace pour des résultats de nettoyage optimisés.
-[DEBIT D'EAU REGLABLE ET RESEVOIR AMOVIBLE] : Avec un débit d'eau réglable à 350 mL/min, cet aspirateur offre un contrôle précis. Les réservoirs d'eau sont amovibles pour un remplissage et un vidage faciles.
-[ACCESSOIRES PRATIQUES ET RANGEMENTS INTEGRES] : Livré avec une brosse amovible et un câble d'alimentation de 3 m, cet aspirateur offre des accessoires pratiques. De plus, le rangement intégré pour les câbles électriques facilite le stockage. Le modèle est compact pour faciliter son rangement dans votre maison.
-[PUISSANCE OPTIMALE ET BROSSE DE RECHANGE INCLUSE] : Avec une puissance de 650 W, cet aspirateur garantit une performance optimale. Une brosse de rechange est également incluse pour une utilisation prolongée.
-[GARANTIE ETENDUE DE 2 ANS] : Bénéficiez d'une garantie étendue de 2 ans, accompagnée d'un atelier SAV en France, offrant ainsi la confiance et la tranquillité d'esprit pour une utilisation prolongée et fiable.</t>
+          <t>NETTOYAGE PUISSANT: Jusqu’à 750 W et env. 15 kPa d’aspiration pour retirer les taches et saletés incrustées des canapés, fauteuils, tapis, moquettes et sièges auto.
+RÉSERVOIRS SÉPARÉS: Réservoir d’eau propre d’env. 1080 ml et cuve d’eau sale d’env. 730 ml pour nettoyer plus longtemps les textiles sans interruptions fréquentes.
+PRATIQUE AU QUOTIDIEN: Poignée de transport, interrupteur marche/arrêt et câble secteur de 5 m offrent une utilisation flexible dans la maison, l’atelier ou la voiture.
+COMPACT ET MOBILE: Format d’env. 32 × 24 × 35 cm et poids d’env. 4,5 kg pour transporter, ranger et utiliser facilement le nettoyeur textile.
+POLYVALENT AVEC ACCESSOIRE: Embout fenêtre inclus pour surfaces vitrées, miroirs et cabines de douche, idéal pour l’entretien de la maison et de l’auto.</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0DBJ2CJ2J</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -18609,13 +18501,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>36271</v>
+        <v>46737</v>
       </c>
       <c r="P43" s="15">
-        <v>93859</v>
+        <v>38735</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -18624,55 +18516,55 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="U43" s="16">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="V43" s="15">
-        <v>4997</v>
+        <v>4827</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
       <c r="Y43" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>64.9</v>
+        <v>69.95</v>
       </c>
       <c r="AA43" s="4"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>1073</v>
+        <v>85</v>
       </c>
       <c r="AE43" s="15">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.0779</v>
+        <v>0.2609</v>
       </c>
       <c r="AH43" s="20">
-        <v>9.53</v>
+        <v>8.89</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>1317</v>
+        <v>155</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -18686,11 +18578,11 @@
         <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>HomeHome by A</t>
+          <t>medionshop-deutschland</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -18700,25 +18592,21 @@
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>Paris 75001 FR</t>
+          <t>Essen 45307 DE</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -18727,54 +18615,42 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD43" s="13"/>
       <c r="BE43" s="13"/>
-      <c r="BF43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>4 Kilogrammes</t>
+          <t>4,5 Kilogrammes</t>
         </is>
       </c>
       <c r="BK43" s="23"/>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>36,5P x 24,5l x 31,8H centimètres</t>
+          <t>24P x 31,7l x 35H centimètres</t>
         </is>
       </c>
       <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>45 x 38 x 29 cm</t>
+          <t>37.6 x 37.1 x 26.9 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
+          <t>37.60 x 37.10 x 26.90 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -18790,52 +18666,52 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Marque: MEDION | Couleur: Gris | Poids de l'article: 4,5 Kilogrammes | Dimensions du produit: 24P x 31,7l x 35H centimètres | Nom de modèle: MD 100122 | Capacité: 1,08 litres | Nombre d'unités: 1.0 unité | Fabricant: MEDION | Nombre d'articles: 1 | Point fort de l’article: Aspirateur eau pour tissus tapis sièges auto, réservoirs propre et sale, embout fenêtre, MD100122</t>
+          <t>Marque: TWOPOINT | Couleur: Blanc | Poids de l'article: 3,8 Kilogrammes | Dimensions du produit: 29,5P x 22l x 33,5H centimètres | Style: Contemporaine | Capacité: 1600 ml | Source d'alimentation: Câble électrique | Fabricant: TWOPOINT | Nombre d'articles: 1</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>MEDION</t>
+          <t>TWOPOINT</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=TWOPOINT</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>MEDION E10 UC Nettoyeur textile injecteur extracteur - 750 W</t>
+          <t>shampouineuse Puissante aspiration de 15 kPa, design léger et portable de seulement 3,8 kg, adapté aux tapis, canapés, sièges de voiture et taches tenaces</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>NETTOYAGE PUISSANT: Jusqu’à 750 W et env. 15 kPa d’aspiration pour retirer les taches et saletés incrustées des canapés, fauteuils, tapis, moquettes et sièges auto.
-RÉSERVOIRS SÉPARÉS: Réservoir d’eau propre d’env. 1080 ml et cuve d’eau sale d’env. 730 ml pour nettoyer plus longtemps les textiles sans interruptions fréquentes.
-PRATIQUE AU QUOTIDIEN: Poignée de transport, interrupteur marche/arrêt et câble secteur de 5 m offrent une utilisation flexible dans la maison, l’atelier ou la voiture.
-COMPACT ET MOBILE: Format d’env. 32 × 24 × 35 cm et poids d’env. 4,5 kg pour transporter, ranger et utiliser facilement le nettoyeur textile.
-POLYVALENT AVEC ACCESSOIRE: Embout fenêtre inclus pour surfaces vitrées, miroirs et cabines de douche, idéal pour l’entretien de la maison et de l’auto.</t>
+          <t>【Aspiration puissante de 15 kPa et nettoyage en profondeur en trois étapes】Shampouineuse est équipé d’un moteur eau et poussière de 500 W offrant une dépression supérieure à 15 kPa. Il convient au nettoyage des salissures quotidiennes et des taches tenaces localisées sur les tapis, les canapés et autres surfaces textiles.
+【Deux réservoirs séparés pour un nettoyage plus hygiénique】Shampouineuse canape dispose d’un réservoir d’eau propre de 1600 ml et d’un réservoir d’eau sale de 1250 ml. L’eau propre et l’eau sale récupérée sont stockées séparément, afin d’éviter de réutiliser l’eau sale pendant le nettoyage. Les deux réservoirs sont amovibles pour faciliter le remplissage, la vidange et le rinçage, même lors du nettoyage continu de grandes surfaces.
+【Câble de 4 m et flexible de 1,6 m pour une plus grande liberté de mouvement】Aspirateur associe un long câble d’alimentation à un flexible souple pour faciliter le nettoyage des canapés, des tapis et des zones situées autour des meubles. Il n’est pas nécessaire de déplacer fréquemment l’appareil ni de changer constamment de prise. Le flexible permet d’atteindre facilement les coins, les bords et les taches localisées.
+【Brosse multifonction et auto-nettoyage des conduits】Aspirateur à eau est équipé d’une brosse standard multifonction de 8,8 cm, offrant un bon équilibre entre efficacité et maniabilité. La brosse d’auto-nettoyage permet de rincer le flexible et les conduits internes après utilisation afin de réduire les résidus d’eau sale. La tête de brosse amovible peut également être rincée directement à l’eau claire.
+【Appareil léger de 3,8 kg, facile à transporter et à ranger】Nettoyeur canapé pèse environ 3,8 kg et mesure seulement 295 × 220 × 334 mm. Sa poignée de transport facilite le déplacement d’une pièce à l’autre. Après utilisation, le flexible et le câble d’alimentation peuvent être rangés directement sur l’appareil afin de réduire l’espace nécessaire.</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HCN3FWXH?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Iur5fvt1L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -18849,13 +18725,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>46737</v>
+        <v>56629</v>
       </c>
       <c r="P44" s="15">
-        <v>38735</v>
+        <v>-17740</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.59</v>
+        <v>-0.81</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -18864,17 +18740,15 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>69</v>
-      </c>
-      <c r="U44" s="16">
-        <v>1.78</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>4827</v>
+        <v>3840</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -18882,37 +18756,37 @@
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>69.95</v>
+        <v>79.99</v>
       </c>
       <c r="AA44" s="4"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="AE44" s="15">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.2609</v>
+        <v>0.1042</v>
       </c>
       <c r="AH44" s="20">
-        <v>8.89</v>
+        <v>8.68</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -18922,15 +18796,13 @@
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44" s="20"/>
-      <c r="AQ44" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ44" s="19"/>
       <c r="AR44" s="19">
         <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>medionshop-deutschland</t>
+          <t>TWOPOINT</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -18945,12 +18817,12 @@
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>Essen 45307 DE</t>
+          <t>Bruchsal 76646 DE</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5O6DZZGWMILN</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
@@ -18971,34 +18843,34 @@
       <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilogrammes</t>
+          <t>3,8 Kilogrammes</t>
         </is>
       </c>
       <c r="BK44" s="23"/>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>24P x 31,7l x 35H centimètres</t>
+          <t>29,5P x 22l x 33,5H centimètres</t>
         </is>
       </c>
       <c r="BM44" s="23"/>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>4.27 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>4.27 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>37.6 x 37.1 x 26.9 cm</t>
+          <t>41.1 x 34.4 x 20.7 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>37.60 x 37.10 x 26.90 cm</t>
+          <t>41.10 x 34.40 x 20.70 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -19014,52 +18886,56 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0HCN3FWXH</t>
-        </is>
-      </c>
-      <c r="D45" s="14"/>
+          <t>B0D2HFLM1C</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Model: StainZapper Pro</t>
+        </is>
+      </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>Marque: TWOPOINT | Couleur: Blanc | Poids de l'article: 3,8 Kilogrammes | Dimensions du produit: 29,5P x 22l x 33,5H centimètres | Style: Contemporaine | Capacité: 1600 ml | Source d'alimentation: Câble électrique | Fabricant: TWOPOINT | Nombre d'articles: 1</t>
+          <t>Marque: HAUSHOF | Couleur: Blanc/Gris Clair | Poids de l'article: 3,85 Kilogrammes | Dimensions du produit: 19,6P x 38,5l x 30H centimètres | Style: StainZapper Pro | Nom de modèle: Nettoyeur de Tapis | Capacité: 1,5 litres | Source d'alimentation: Avec cordon secteur | Fabricant: Hang Zhou Great Star Industrial Co.,Ltd | UPC: 820909606536</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>TWOPOINT</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=TWOPOINT</t>
+          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>shampouineuse Puissante aspiration de 15 kPa, design léger et portable de seulement 3,8 kg, adapté aux tapis, canapés, sièges de voiture et taches tenaces</t>
+          <t>HAUSHOF StainZapper Pro, Shampouineuse Canapé avec Moteur Puissant de 450 W</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>【Aspiration puissante de 15 kPa et nettoyage en profondeur en trois étapes】Shampouineuse est équipé d’un moteur eau et poussière de 500 W offrant une dépression supérieure à 15 kPa. Il convient au nettoyage des salissures quotidiennes et des taches tenaces localisées sur les tapis, les canapés et autres surfaces textiles.
-【Deux réservoirs séparés pour un nettoyage plus hygiénique】Shampouineuse canape dispose d’un réservoir d’eau propre de 1600 ml et d’un réservoir d’eau sale de 1250 ml. L’eau propre et l’eau sale récupérée sont stockées séparément, afin d’éviter de réutiliser l’eau sale pendant le nettoyage. Les deux réservoirs sont amovibles pour faciliter le remplissage, la vidange et le rinçage, même lors du nettoyage continu de grandes surfaces.
-【Câble de 4 m et flexible de 1,6 m pour une plus grande liberté de mouvement】Aspirateur associe un long câble d’alimentation à un flexible souple pour faciliter le nettoyage des canapés, des tapis et des zones situées autour des meubles. Il n’est pas nécessaire de déplacer fréquemment l’appareil ni de changer constamment de prise. Le flexible permet d’atteindre facilement les coins, les bords et les taches localisées.
-【Brosse multifonction et auto-nettoyage des conduits】Aspirateur à eau est équipé d’une brosse standard multifonction de 8,8 cm, offrant un bon équilibre entre efficacité et maniabilité. La brosse d’auto-nettoyage permet de rincer le flexible et les conduits internes après utilisation afin de réduire les résidus d’eau sale. La tête de brosse amovible peut également être rincée directement à l’eau claire.
-【Appareil léger de 3,8 kg, facile à transporter et à ranger】Nettoyeur canapé pèse environ 3,8 kg et mesure seulement 295 × 220 × 334 mm. Sa poignée de transport facilite le déplacement d’une pièce à l’autre. Après utilisation, le flexible et le câble d’alimentation peuvent être rangés directement sur l’appareil afin de réduire l’espace nécessaire.</t>
+          <t>Aspiration puissante : Moteur amélioré de 450 W avec une puissance accrue pour une force d'aspiration plus élevée de 12 kPa. La poussière et l'eau sale sont aspirées simultanément et nettoient les textiles sans effort. Convient pour le nettoyage des tapis, canapés, coussins, escaliers, sièges de voiture, tissus, etc
+Capacité accrue du réservoir d'eau : Capacité du réservoir d'eau propre : 1500 ml, capacité du réservoir d'eau sale : 800 ml. La capacité accrue du réservoir d'eau réduit le nombre de remplissages et de vidages et améliore l'efficacité du nettoyage
+Conception de flotteur : Le réservoir d'eau sale est équipé de flotteurs qui servent de dispositif de sécurité pour empêcher les fuites dues à l'aspiration d'une trop grande quantité d'eaux usées. Lorsque les eaux usées atteignent leur capacité maximale, veuillez les vider à temps pour éviter que l'appareil ne cesse d'aspirer
+Tuyau prolongé et tête de brosse améliorée : Avec un tuyau intégré de 160 cm de long pour éliminer les taches. Dispose également d'une fonction de rangement séparée pour le tuyau : enroulez le tuyau sur le support pour le ranger facilement. Avec deux têtes de brosse, une grande tête de brosse et une brosse spéciale pour les joints des canapés, qui fonctionnent parfaitement ensemble et conviennent au nettoyage des taches dans tous les coins
+Idéal pour un nettoyage en profondeur : Rinçage, brossage et aspiration - trois fonctions en une. Le rinçage en profondeur dissout la couche interne de saleté, la brosse haute densité peut pénétrer dans les interstices des fibres, brosser les saletés tenaces, et enfin, grâce à une aspiration puissante, aspirer la poussière et l'eau sale, pour un séchage rapide après le lavage sans longue attente. En cas de salissures tenaces, vous pouvez ajouter notre détergent fourni dans le réservoir d'eau propre dans un rapport de 1:33 entre le détergent et l'eau (à l'aide du gobelet doseur de 50 ml fourni) pour obtenir un nettoyage en profondeur parfait</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HCN3FWXH?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0D2HFLM1C?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Iur5fvt1L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0HCN3FWXH</t>
+          <t>B0DN6BPLYN</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -19073,13 +18949,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>56629</v>
+        <v>52619</v>
       </c>
       <c r="P45" s="15">
-        <v>-17740</v>
+        <v>51665</v>
       </c>
       <c r="Q45" s="16">
-        <v>-0.81</v>
+        <v>0.39</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -19088,53 +18964,55 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>48</v>
-      </c>
-      <c r="U45" s="16"/>
+        <v>17</v>
+      </c>
+      <c r="U45" s="16">
+        <v>0.26</v>
+      </c>
       <c r="V45" s="15">
-        <v>3840</v>
+        <v>1530</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45" s="20">
-        <v>79.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA45" s="4"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>8</v>
+        <v>728</v>
       </c>
       <c r="AE45" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.1042</v>
+        <v>0.1765</v>
       </c>
       <c r="AH45" s="20">
         <v>8.68</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>45</v>
+        <v>794</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -19144,13 +19022,15 @@
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45" s="20"/>
-      <c r="AQ45" s="19"/>
+      <c r="AQ45" s="19">
+        <v>10</v>
+      </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>TWOPOINT</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
@@ -19158,21 +19038,9 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU45" s="13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AV45" s="14" t="inlineStr">
-        <is>
-          <t>Bruchsal 76646 DE</t>
-        </is>
-      </c>
-      <c r="AW45" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5O6DZZGWMILN</t>
-        </is>
-      </c>
+      <c r="AU45" s="13"/>
+      <c r="AV45" s="14"/>
+      <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
@@ -19183,47 +19051,55 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
-      <c r="BF45" s="13"/>
+      <c r="BF45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
       <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>3,8 Kilogrammes</t>
+          <t>3,85 Kilogrammes</t>
         </is>
       </c>
       <c r="BK45" s="23"/>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>29,5P x 22l x 33,5H centimètres</t>
+          <t>19,6P x 38,5l x 30H centimètres</t>
         </is>
       </c>
       <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>4.27 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>4.27 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>41.1 x 34.4 x 20.7 cm</t>
+          <t>44.4 x 33.9 x 20 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>41.10 x 34.40 x 20.70 cm</t>
+          <t>44.40 x 33.90 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -19234,56 +19110,57 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0HFW8M5VH</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Model: StainZapper Pro</t>
+          <t>Set name: Uwant Y100 Steam</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Marque: HAUSHOF | Couleur: Blanc/Gris Clair | Poids de l'article: 3,85 Kilogrammes | Dimensions du produit: 19,6P x 38,5l x 30H centimètres | Style: StainZapper Pro | Nom de modèle: Nettoyeur de Tapis | Capacité: 1,5 litres | Source d'alimentation: Avec cordon secteur | Fabricant: Hang Zhou Great Star Industrial Co.,Ltd | UPC: 820909606536</t>
+          <t>Marque: uwant | Couleur: Blanc | Poids de l'article: 2,5 Kilogrammes | Dimensions du produit: 25P x 45l x 35H millimètres | Nom de modèle: Y100 | Capacité: 1,2 litres | Source d'alimentation: Câble électrique | Nombre d’emballages: 1 | Nombre d'unités: 1 Compteur | Fabricant: Uwant</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Pro, Shampouineuse Canapé avec Moteur Puissant de 450 W</t>
+          <t>Uwant Y100S Shampouineuse, Lave et Sèche, 1750W, 18kPa, Réservoir 2.4L.</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Aspiration puissante : Moteur amélioré de 450 W avec une puissance accrue pour une force d'aspiration plus élevée de 12 kPa. La poussière et l'eau sale sont aspirées simultanément et nettoient les textiles sans effort. Convient pour le nettoyage des tapis, canapés, coussins, escaliers, sièges de voiture, tissus, etc
-Capacité accrue du réservoir d'eau : Capacité du réservoir d'eau propre : 1500 ml, capacité du réservoir d'eau sale : 800 ml. La capacité accrue du réservoir d'eau réduit le nombre de remplissages et de vidages et améliore l'efficacité du nettoyage
-Conception de flotteur : Le réservoir d'eau sale est équipé de flotteurs qui servent de dispositif de sécurité pour empêcher les fuites dues à l'aspiration d'une trop grande quantité d'eaux usées. Lorsque les eaux usées atteignent leur capacité maximale, veuillez les vider à temps pour éviter que l'appareil ne cesse d'aspirer
-Tuyau prolongé et tête de brosse améliorée : Avec un tuyau intégré de 160 cm de long pour éliminer les taches. Dispose également d'une fonction de rangement séparée pour le tuyau : enroulez le tuyau sur le support pour le ranger facilement. Avec deux têtes de brosse, une grande tête de brosse et une brosse spéciale pour les joints des canapés, qui fonctionnent parfaitement ensemble et conviennent au nettoyage des taches dans tous les coins
-Idéal pour un nettoyage en profondeur : Rinçage, brossage et aspiration - trois fonctions en une. Le rinçage en profondeur dissout la couche interne de saleté, la brosse haute densité peut pénétrer dans les interstices des fibres, brosser les saletés tenaces, et enfin, grâce à une aspiration puissante, aspirer la poussière et l'eau sale, pour un séchage rapide après le lavage sans longue attente. En cas de salissures tenaces, vous pouvez ajouter notre détergent fourni dans le réservoir d'eau propre dans un rapport de 1:33 entre le détergent et l'eau (à l'aide du gobelet doseur de 50 ml fourni) pour obtenir un nettoyage en profondeur parfait</t>
+          <t>【Lavage &amp; Aspiration + 3 Modes, Puissance et Désinfection】Nettoyeur à vapeur pour canapés et tissus, 1750 W et aspiration 18 kPa. Propose mode eau froide, mode eau chaude (65°C, chauffe 10s, débit 360±40 ml/min) et mode vapeur (100°C, chauffe 30s, débit vapeur 35+5 ml/min). Efficacité antibactérienne 99,9%, élimine les taches tenaces (graisse, café, urine) et aspire rapidement, laissant la surface sèche.
+【Ensemble de Brosses Polyvalent】Inclut brosse standard/large 2en1 avec plateau en silicone et poils réversibles, buse d'eau visible pour contrôler le débit. Adapté aux tissus, soie, cuir, etc. Plus brosse à fente vapeur, brosse ronde vapeur, brosse à chaussures et 500 ml de liquide nettoyant – pour nettoyage en profondeur et désinfection sur tapis, canapés, sièges auto, vitres, sols et taches tenaces.
+【Réservoirs Doubles Intégrés – Auto-nettoyant Anti-obstruction】Deux réservoirs indépendants de 1,2 L chacun : un pour eau propre, un pour eau sale. Remplir et vider en un geste. Câble 5 m et tuyau 1,5 m pour une grande portée. Après utilisation, mettre le couvercle auto-nettoyant – le tuyau est rincé automatiquement, évitant saletés et odeurs. Attention : ne pas dépasser le repère MAX, sinon le nettoyage s'arrête automatiquement.
+【Léger et Compact – Rangement Facile】Poids 3,4 kg – facile à déplacer, même pour les femmes. Dimensions 35,6 x 18,3 x 31 cm – peu encombrant, se range dans n'importe quel placard.
+【Pour Salissures Solides et Liquides – Polyvalent】Élimine efficacement les déversements solides/liquides et les poils d'animaux. Nettoie rapidement surfaces molles comme tissus d'ameublement, tapis, canapés, voitures, escaliers, matelas, ainsi que surfaces dures comme vitres (maison/voiture) et sols – pas de coins oubliés.
+【Qualité Professionnelle – Garantie 2 Ans】Qualité testée rigoureusement, garantie constructeur 2 ans. Inclus manuel d'instructions détaillé et service client professionnel – utilisation sans souci.</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0D2HFLM1C?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFW8M5VH?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0DN6BPLYN</t>
+          <t>B0HJW7LPHT</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -19297,13 +19174,11 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>52619</v>
-      </c>
-      <c r="P46" s="15">
-        <v>51665</v>
-      </c>
+        <v>15568</v>
+      </c>
+      <c r="P46" s="15"/>
       <c r="Q46" s="16">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -19312,17 +19187,15 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>17</v>
-      </c>
-      <c r="U46" s="16">
-        <v>0.26</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>1530</v>
+        <v>850</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
@@ -19330,37 +19203,37 @@
         <v>2</v>
       </c>
       <c r="Z46" s="20">
-        <v>89.99</v>
+        <v>169.99</v>
       </c>
       <c r="AA46" s="4"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>728</v>
+        <v>263</v>
       </c>
       <c r="AE46" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>8.68</v>
+        <v>9.32</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>794</v>
+        <v>31</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -19378,7 +19251,7 @@
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>TIMO Smart Home</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -19386,9 +19259,21 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>KWUN TONG KOWLOON 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
@@ -19415,39 +19300,39 @@
       <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>3,85 Kilogrammes</t>
+          <t>2,5 Kilogrammes</t>
         </is>
       </c>
       <c r="BK46" s="23"/>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>19,6P x 38,5l x 30H centimètres</t>
+          <t>25P x 45l x 35H millimètres</t>
         </is>
       </c>
       <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>6.26 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>6.26 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.9 x 20 cm</t>
+          <t>48 x 37.2 x 26.6 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.90 x 20.00 cm</t>
+          <t>48.00 x 37.20 x 26.60 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -19458,57 +19343,52 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0HFW8M5VH</t>
+          <t>B0F9XDVZ4N</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Set name: Uwant Y100 Steam</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Marque: uwant | Couleur: Blanc | Poids de l'article: 2,5 Kilogrammes | Dimensions du produit: 25P x 45l x 35H millimètres | Nom de modèle: Y100 | Capacité: 1,2 litres | Source d'alimentation: Câble électrique | Nombre d’emballages: 1 | Nombre d'unités: 1 Compteur | Fabricant: Uwant</t>
-        </is>
-      </c>
+          <t>Couleur: 580mL*2</t>
+        </is>
+      </c>
+      <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>NQILGDOH</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NQILGDOH</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100S Shampouineuse, Lave et Sèche, 1750W, 18kPa, Réservoir 2.4L.</t>
+          <t>Liquide Nettoyant Spécial Sols. Compatible Avec Narwal Freo Z Ultra/Freo Z10. Détergent Nettoyant 580 Ml.(580mL*2)</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>【Lavage &amp; Aspiration + 3 Modes, Puissance et Désinfection】Nettoyeur à vapeur pour canapés et tissus, 1750 W et aspiration 18 kPa. Propose mode eau froide, mode eau chaude (65°C, chauffe 10s, débit 360±40 ml/min) et mode vapeur (100°C, chauffe 30s, débit vapeur 35+5 ml/min). Efficacité antibactérienne 99,9%, élimine les taches tenaces (graisse, café, urine) et aspire rapidement, laissant la surface sèche.
-【Ensemble de Brosses Polyvalent】Inclut brosse standard/large 2en1 avec plateau en silicone et poils réversibles, buse d'eau visible pour contrôler le débit. Adapté aux tissus, soie, cuir, etc. Plus brosse à fente vapeur, brosse ronde vapeur, brosse à chaussures et 500 ml de liquide nettoyant – pour nettoyage en profondeur et désinfection sur tapis, canapés, sièges auto, vitres, sols et taches tenaces.
-【Réservoirs Doubles Intégrés – Auto-nettoyant Anti-obstruction】Deux réservoirs indépendants de 1,2 L chacun : un pour eau propre, un pour eau sale. Remplir et vider en un geste. Câble 5 m et tuyau 1,5 m pour une grande portée. Après utilisation, mettre le couvercle auto-nettoyant – le tuyau est rincé automatiquement, évitant saletés et odeurs. Attention : ne pas dépasser le repère MAX, sinon le nettoyage s'arrête automatiquement.
-【Léger et Compact – Rangement Facile】Poids 3,4 kg – facile à déplacer, même pour les femmes. Dimensions 35,6 x 18,3 x 31 cm – peu encombrant, se range dans n'importe quel placard.
-【Pour Salissures Solides et Liquides – Polyvalent】Élimine efficacement les déversements solides/liquides et les poils d'animaux. Nettoie rapidement surfaces molles comme tissus d'ameublement, tapis, canapés, voitures, escaliers, matelas, ainsi que surfaces dures comme vitres (maison/voiture) et sols – pas de coins oubliés.
-【Qualité Professionnelle – Garantie 2 Ans】Qualité testée rigoureusement, garantie constructeur 2 ans. Inclus manuel d'instructions détaillé et service client professionnel – utilisation sans souci.</t>
+          <t>【Convient à tous les types d'environnements de sol】: Nettoyez efficacement une variété de surfaces dures dans votre maison, y compris le marbre, le carrelage et les sols scellés.
+Parfum naturel : Le parfum naturel de citron est doux, naturel et frais. Il élimine les odeurs du sol et laisse un léger parfum naturel sur le sol.
+【Facile à éliminer toutes sortes de taches tenaces】: Doux, peu moussant, il élimine rapidement la saleté accumulée, la graisse, l'eau, les traces de pas et les taches collantes, laissant votre sol étincelant et naturellement frais.
+【Nettoyage efficace】Il a une bonne surface dure et une bonne capacité de nettoyage, et la surface dure est brillante et texturée après le nettoyage.
+Modèle compatible : Solution nettoyante for sols, saveur citron, 580 ml. Compatible avec Narwal Freo Z Ultra / Freo Z10. Pièces détachées for aspirateurs robots.</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HFW8M5VH?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9XDVZ4N?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31dfBZGIZML._SX600_SY600_CR,0,0,600,600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0HJW7LPHT</t>
+          <t>B0F9XHDTPB</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -19522,11 +19402,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>15568</v>
-      </c>
-      <c r="P47" s="15"/>
+        <v>22905</v>
+      </c>
+      <c r="P47" s="15">
+        <v>174269</v>
+      </c>
       <c r="Q47" s="16">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -19535,53 +19417,53 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>5</v>
-      </c>
-      <c r="U47" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="U47" s="16">
+        <v>6.75</v>
+      </c>
       <c r="V47" s="15">
-        <v>850</v>
+        <v>798</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z47" s="20">
-        <v>169.99</v>
+        <v>39.89</v>
       </c>
       <c r="AA47" s="4"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="AE47" s="15">
         <v>0</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
       </c>
-      <c r="AH47" s="20">
-        <v>9.32</v>
-      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>31</v>
+        <v>490</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
@@ -19592,14 +19474,14 @@
       <c r="AO47" s="13"/>
       <c r="AP47" s="20"/>
       <c r="AQ47" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>TIMO Smart Home</t>
+          <t>jitao0</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
@@ -19609,17 +19491,17 @@
       </c>
       <c r="AU47" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>KWUN TONG KOWLOON 999077 HK</t>
+          <t>浏阳市 410000 CN</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FTADH5UN7C2O</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
@@ -19627,62 +19509,38 @@
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC47" s="13"/>
+      <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
-      <c r="BF47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
       <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>2,5 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK47" s="23"/>
+          <t>50 grammes</t>
+        </is>
+      </c>
+      <c r="BK47" s="23" t="inlineStr">
+        <is>
+          <t>50.00 g</t>
+        </is>
+      </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>25P x 45l x 35H millimètres</t>
-        </is>
-      </c>
-      <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>6.26 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>6.26 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>48 x 37.2 x 26.6 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>48.00 x 37.20 x 26.60 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>2,54 x 2,54 x 2,54 cm</t>
+        </is>
+      </c>
+      <c r="BM47" s="23" t="inlineStr">
+        <is>
+          <t>2.54 x 2.54 x 2.54 cm</t>
+        </is>
+      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -19691,52 +19549,52 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0F9XDVZ4N</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>Couleur: 580mL*2</t>
-        </is>
-      </c>
-      <c r="E48" s="14"/>
+          <t>B0FN7HZHWY</t>
+        </is>
+      </c>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Marque: Livatro | Forme de l'article: Liquide | Parfum: Fraîcheur | Usages spécifiques pour le produit: Tapis | Caractéristique du matériau: Respectueux de l'environnement | Nombre d'unités: 500.0 millilitre | Nombre d'articles: 1 | Contient du contenu liquide: Oui | Fabricant: Livatro | UPC: 850057188837</t>
+        </is>
+      </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>NQILGDOH</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NQILGDOH</t>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Liquide Nettoyant Spécial Sols. Compatible Avec Narwal Freo Z Ultra/Freo Z10. Détergent Nettoyant 580 Ml.(580mL*2)</t>
+          <t>Livatro Nettoyant Tapis et Canapés, Concentré 1:30, Faible Mousse, 500 ml</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>【Convient à tous les types d'environnements de sol】: Nettoyez efficacement une variété de surfaces dures dans votre maison, y compris le marbre, le carrelage et les sols scellés.
-Parfum naturel : Le parfum naturel de citron est doux, naturel et frais. Il élimine les odeurs du sol et laisse un léger parfum naturel sur le sol.
-【Facile à éliminer toutes sortes de taches tenaces】: Doux, peu moussant, il élimine rapidement la saleté accumulée, la graisse, l'eau, les traces de pas et les taches collantes, laissant votre sol étincelant et naturellement frais.
-【Nettoyage efficace】Il a une bonne surface dure et une bonne capacité de nettoyage, et la surface dure est brillante et texturée après le nettoyage.
-Modèle compatible : Solution nettoyante for sols, saveur citron, 580 ml. Compatible avec Narwal Freo Z Ultra / Freo Z10. Pièces détachées for aspirateurs robots.</t>
+          <t>Compatibilité étendue pour un nettoyage en profondeur: Spécialement conçu pour la shampouineuse Livatro pour tissus d’ameublement (LVCUCM001/002). Idéal pour canapés, tapis/moquettes, rideaux, matelas et intérieurs de voiture. Élimine les taches incrustées et les mauvaises odeurs pour des textiles comme neufs.
+Action puissante contre les taches et les odeurs: Ce nettoyeur canapé tissu cible et décompose rapidement les taches courantes (café, graisse, traces d’animaux, boue), tout en aidant à neutraliser les odeurs au cœur des fibres. Nettoyage et désodorisation en une seule étape. Laisse les textiles frais, sans odeur de renfermé.
+Formule douce qui préserve couleurs et textures: Nettoie efficacement sans agresser les fibres ni les colorants, pour conserver l’aspect et le toucher des tissus. Test préalable recommandé sur une zone peu visible.
+Concentré, faible mousse – rapide et efficace: Dilution 1:30 (1 dose de produit pour 30 doses d’eau). La faible mousse facilite l’extraction, limite les résidus et accélère le séchage — un gain de temps et de produit.
+Mode d’emploi en 3 étapes:Avec votre shampouineuse canape : Diluer et verser dans le réservoir d’eau claire → Vaporiser/Brosser → Extraire l’eau sale. Pour un résultat optimal, terminer par un rinçage à l’eau claire. Conserver hors de portée des enfants et des animaux. Ne pas mélanger avec de l’eau de Javel (chlore) ni avec des produits à base d’ammoniaque.</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9XDVZ4N?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN7HZHWY?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31dfBZGIZML._SX600_SY600_CR,0,0,600,600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0F9XHDTPB</t>
+          <t>B0FN7HZHWY</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -19750,13 +19608,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>22905</v>
+        <v>56677</v>
       </c>
       <c r="P48" s="15">
-        <v>174269</v>
+        <v>-88339</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.76</v>
+        <v>-0.69</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -19765,53 +19623,55 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="U48" s="16">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="V48" s="15">
-        <v>798</v>
+        <v>518</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>39.89</v>
+        <v>13.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AE48" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AG48" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="20"/>
+        <v>0.1081</v>
+      </c>
+      <c r="AH48" s="20">
+        <v>5.98</v>
+      </c>
       <c r="AI48" s="16">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>490</v>
+        <v>292</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -19822,14 +19682,14 @@
       <c r="AO48" s="13"/>
       <c r="AP48" s="20"/>
       <c r="AQ48" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
         <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>jitao0</t>
+          <t>HOORAY Group</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -19839,17 +19699,17 @@
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>浏阳市 410000 CN</t>
+          <t>HK 999077 HK</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FTADH5UN7C2O</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -19857,38 +19717,66 @@
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD48" s="13"/>
       <c r="BE48" s="13"/>
-      <c r="BF48" s="13"/>
+      <c r="BF48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>50 grammes</t>
+          <t>600 grammes</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>600.00 g</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>2,54 x 2,54 x 2,54 cm</t>
+          <t>20 x 9,3 x 6,5 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>2.54 x 2.54 x 2.54 cm</t>
-        </is>
-      </c>
-      <c r="BN48" s="23"/>
-      <c r="BO48" s="23"/>
-      <c r="BP48" s="23"/>
-      <c r="BQ48" s="23"/>
-      <c r="BR48" s="13"/>
+          <t>20.00 x 9.30 x 6.50 cm</t>
+        </is>
+      </c>
+      <c r="BN48" s="23" t="inlineStr">
+        <is>
+          <t>630 g</t>
+        </is>
+      </c>
+      <c r="BO48" s="23" t="inlineStr">
+        <is>
+          <t>630.00 g</t>
+        </is>
+      </c>
+      <c r="BP48" s="23" t="inlineStr">
+        <is>
+          <t>20 x 9.3 x 6.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ48" s="23" t="inlineStr">
+        <is>
+          <t>20.00 x 9.30 x 6.50 cm</t>
+        </is>
+      </c>
+      <c r="BR48" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -19897,52 +19785,57 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
-        </is>
-      </c>
-      <c r="D49" s="14"/>
+          <t>B0HFJG9Z8G</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Couleur: Blanc</t>
+        </is>
+      </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>Marque: Livatro | Forme de l'article: Liquide | Parfum: Fraîcheur | Usages spécifiques pour le produit: Tapis | Caractéristique du matériau: Respectueux de l'environnement | Nombre d'unités: 500.0 millilitre | Nombre d'articles: 1 | Contient du contenu liquide: Oui | Fabricant: Livatro | UPC: 850057188837</t>
+          <t>Marque: STARRYBOT | Couleur: Blanc | Poids de l'article: 4,6 Kilogrammes | Dimensions du produit: 40P x 33l x 19H centimètres | Capacité: 2 litres | Disponibilité de pièces détachées dans l’UE: 10 Ans | Nombre d'unités: 1.0 unité | Fabricant: STARRYBOT | Nombre d'articles: 1 | Point fort de l’article: Pour sièges auto, tissus d’ameublement et taches d’animaux, avec aspiration puissante et nettoyage ciblé.</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>STARRYBOT</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Livatro Nettoyant Tapis et Canapés, Concentré 1:30, Faible Mousse, 500 ml</t>
+          <t>STARRYBOT Shampouineuse Canapé Tapis Portable 22kPa, Détacheur Tissus Blanc</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>Compatibilité étendue pour un nettoyage en profondeur: Spécialement conçu pour la shampouineuse Livatro pour tissus d’ameublement (LVCUCM001/002). Idéal pour canapés, tapis/moquettes, rideaux, matelas et intérieurs de voiture. Élimine les taches incrustées et les mauvaises odeurs pour des textiles comme neufs.
-Action puissante contre les taches et les odeurs: Ce nettoyeur canapé tissu cible et décompose rapidement les taches courantes (café, graisse, traces d’animaux, boue), tout en aidant à neutraliser les odeurs au cœur des fibres. Nettoyage et désodorisation en une seule étape. Laisse les textiles frais, sans odeur de renfermé.
-Formule douce qui préserve couleurs et textures: Nettoie efficacement sans agresser les fibres ni les colorants, pour conserver l’aspect et le toucher des tissus. Test préalable recommandé sur une zone peu visible.
-Concentré, faible mousse – rapide et efficace: Dilution 1:30 (1 dose de produit pour 30 doses d’eau). La faible mousse facilite l’extraction, limite les résidus et accélère le séchage — un gain de temps et de produit.
-Mode d’emploi en 3 étapes:Avec votre shampouineuse canape : Diluer et verser dans le réservoir d’eau claire → Vaporiser/Brosser → Extraire l’eau sale. Pour un résultat optimal, terminer par un rinçage à l’eau claire. Conserver hors de portée des enfants et des animaux. Ne pas mélanger avec de l’eau de Javel (chlore) ni avec des produits à base d’ammoniaque.</t>
+          <t>[PUISSANCE D'ASPIRATION AMÉLIORÉE 22 KPA] Doté d'une aspiration ultra-puissante de 22 000 Pa, ce nettoyeur élimine sans effort les taches tenaces, les liquides renversés et les saletés incrustées dans les fibres textiles.
+[Nettoyage précis avec 3 outils] L’outil manuel de 7,6 cm cible les petites taches, l’outil large de 12,7 cm couvre les zones plus étendues, tandis que l’outil CreviceCollector intégré atteint les interstices
+[Double réservoir pratique] Le réservoir d’eau propre d’environ 1,77 L et le réservoir d’eau sale d’environ 1,18 L séparent l’eau propre de l’eau usée. Doté d’un rayon d’action de 5,7 m, il facilite le nettoyage sur de grandes surfaces.
+[Compacte et portable] Avec un poids d’environ 4,6 kg, une poignée amovible et un format facile à ranger, cette shampouineuse canapé se transporte aisément entre la maison, le garage et la voiture.
+[Pour la maison et la voiture] Conçue pour les tapis, canapés, tissus d’ameublement, sièges auto et taches d’animaux, elle accompagne l’entretien quotidien de votre intérieur, avec une garantie d’un an pour plus
+[Service Après‑Vente et Garantie] STARRYBOT offre une garantie constructeur d’un an. Notre équipe du service client disponible 24 h/24 et 7 j/7 propose une assistance rapide et sans tracas</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN7HZHWY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFJG9Z8G?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
+          <t>B0HL67B91S</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -19956,13 +19849,11 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>56677</v>
-      </c>
-      <c r="P49" s="15">
-        <v>-88339</v>
-      </c>
+        <v>11396</v>
+      </c>
+      <c r="P49" s="15"/>
       <c r="Q49" s="16">
-        <v>-0.69</v>
+        <v>0</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19971,56 +19862,38 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>37</v>
-      </c>
-      <c r="U49" s="16">
-        <v>7.5</v>
-      </c>
-      <c r="V49" s="15">
-        <v>518</v>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T49" s="15"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="19">
         <v>1</v>
       </c>
-      <c r="Z49" s="20">
-        <v>13.99</v>
-      </c>
+      <c r="Z49" s="20"/>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>28</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>4</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.1081</v>
-      </c>
-      <c r="AH49" s="20">
-        <v>5.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>292</v>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
       <c r="AM49" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -20029,37 +19902,17 @@
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="20"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>HOORAY Group</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
       <c r="AT49" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>HK 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
-        </is>
-      </c>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
@@ -20070,7 +19923,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13"/>
+      <c r="BD49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13" t="inlineStr">
         <is>
@@ -20082,419 +19939,21 @@
       <c r="BI49" s="23"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>600 grammes</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>600.00 g</t>
-        </is>
-      </c>
+          <t>4,6 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK49" s="23"/>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>20 x 9,3 x 6,5 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
-        </is>
-      </c>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>630 g</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>630.00 g</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>20 x 9.3 x 6.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0CFRBWJKR</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Style: Revolution Hydrosteam</t>
-        </is>
-      </c>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>Marque: Bissell | Couleur: Noir, Titane, Bleu Cobalt | Poids de l'article: 10,2 Kilogrammes | Dimensions du produit: 32P x 45l x 1105H centimètres | Style: Revolution Hydrosteam | Nom de modèle: BISSELL | Capacité: 3,8 litres | Source d'alimentation: électrique | Fabricant: BISSELL | UPC: 011120271454</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Bissell</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frnull</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>BISSELL Revolution HydroSteam Nettoyeur Vapeur 1300W 3670N</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>TECHNOLOGIE HYDROSTEAM: La technologie révolutionnaire HydroSteam élimine facilement les saletés incrustées, collantes et grasses. Profitez d'un nettoyage plus profond et plus complet de vos tapis et tissus d'ameublement avec cette nettoyeur vapeur
-MODE SÉCHAGE RAPIDE: Le nettoyeur canapé tissu nettoie et rafraîchit vos tapis et coureurs, les laissant secs en environ 30 minutes* Parfait pour une mise à jour rapide avant l'arrivée des invités
-MODE PRÉTRAITEMENT À LA VAPEUR: Utilisez le mode de pré-pulvérisation à la vapeur pour détacher efficacement les saletés tenaces, incrustées et collantes avant le nettoyage principal
-DOUBLE BROSSES ROTATIVES DIRTLIFTER: Deux puissantes brosses rotatives à six rangées de poils pénètrent profondément dans vos tapis pour éliminer les taches les plus tenaces et la saleté incrustée
-DEUX RÉSERVOIRS SÉPARÉS: Le nettoyeur tapis avec des réservoirs séparés pour l'eau propre et l'eau sale, vous nettoyez toujours avec de l'eau propre, évitant ainsi la réintroduction de la saleté
-NETTOYAGE COMPLET: Le nettoyeur vapeur pour canapé a une système de tuyau de 2,4 m inclus et l'outil Tough Stain permettent un nettoyage approfondi des zones difficiles d'accès telles que les escaliers et les meubles rembourrés
-MODES DE NETTOYAGE POLYVALENTS: Le Revolution HydroSteam propose différents modes tels que Steam Pretreat, SteamWash Max Clean et Quick Dry pour répondre à diverses exigences de nettoyage dans votre maison
-ACCESSOIRES COMPLETS INCLUS: Comprend l'outil pour taches tenaces de 8 cm, un tuyau pour le nettoyage au-dessus du sol, un outil de nettoyage des buses, un sac en filet et 3 puissantes solutions de nettoyage BISSELL (236 ml chacune)</t>
-        </is>
-      </c>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0CFRBWJKR?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41JShjmKqDL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0GY9WGM7P</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>55905</v>
-      </c>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16">
-        <v>0</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>341.52</v>
-      </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>667</v>
-      </c>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13"/>
-      <c r="AL50" s="19"/>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN50" s="13" t="inlineStr">
-        <is>
-          <t>3天</t>
-        </is>
-      </c>
-      <c r="AO50" s="13"/>
-      <c r="AP50" s="20">
-        <v>186.1</v>
-      </c>
-      <c r="AQ50" s="19"/>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>10,2 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK50" s="23"/>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>32P x 45l x 1105H centimètres</t>
-        </is>
-      </c>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50" s="23"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJG9Z8G</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Couleur: Blanc</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Marque: STARRYBOT | Couleur: Blanc | Poids de l'article: 4,6 Kilogrammes | Dimensions du produit: 40P x 33l x 19H centimètres | Capacité: 2 litres | Disponibilité de pièces détachées dans l’UE: 10 Ans | Nombre d'unités: 1.0 unité | Fabricant: STARRYBOT | Nombre d'articles: 1 | Point fort de l’article: Pour sièges auto, tissus d’ameublement et taches d’animaux, avec aspiration puissante et nettoyage ciblé.</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>STARRYBOT</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>STARRYBOT Shampouineuse Canapé Tapis Portable 22kPa, Détacheur Tissus Blanc</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>[PUISSANCE D'ASPIRATION AMÉLIORÉE 22 KPA] Doté d'une aspiration ultra-puissante de 22 000 Pa, ce nettoyeur élimine sans effort les taches tenaces, les liquides renversés et les saletés incrustées dans les fibres textiles.
-[Nettoyage précis avec 3 outils] L’outil manuel de 7,6 cm cible les petites taches, l’outil large de 12,7 cm couvre les zones plus étendues, tandis que l’outil CreviceCollector intégré atteint les interstices
-[Double réservoir pratique] Le réservoir d’eau propre d’environ 1,77 L et le réservoir d’eau sale d’environ 1,18 L séparent l’eau propre de l’eau usée. Doté d’un rayon d’action de 5,7 m, il facilite le nettoyage sur de grandes surfaces.
-[Compacte et portable] Avec un poids d’environ 4,6 kg, une poignée amovible et un format facile à ranger, cette shampouineuse canapé se transporte aisément entre la maison, le garage et la voiture.
-[Pour la maison et la voiture] Conçue pour les tapis, canapés, tissus d’ameublement, sièges auto et taches d’animaux, elle accompagne l’entretien quotidien de votre intérieur, avec une garantie d’un an pour plus
-[Service Après‑Vente et Garantie] STARRYBOT offre une garantie constructeur d’un an. Notre équipe du service client disponible 24 h/24 et 7 j/7 propose une assistance rapide et sans tracas</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HFJG9Z8G?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HL67B91S</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>11396</v>
-      </c>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16">
-        <v>0</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>372</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.8</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="20"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>4,6 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
           <t>40P x 33l x 19H centimètres</t>
         </is>
       </c>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
+      <c r="BM49" s="23"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20734,145 +20193,131 @@
     <hyperlink ref="M33" r:id="rId232" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N33" r:id="rId233"/>
     <hyperlink ref="AW33" r:id="rId234" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
-    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.fr/dp/B07999DC2C?psc=1"/>
-    <hyperlink ref="K34" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.fr/dp/B09XN93JDC"/>
+    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
+    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
+    <hyperlink ref="K34" r:id="rId238" tooltip="https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0HD1BJXTZ"/>
     <hyperlink ref="M34" r:id="rId240" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N34" r:id="rId241"/>
-    <hyperlink ref="C35" r:id="rId242" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
-    <hyperlink ref="G35" r:id="rId243" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
-    <hyperlink ref="K35" r:id="rId245" tooltip="https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId246" tooltip="https://www.amazon.fr/dp/B0HD1BJXTZ"/>
-    <hyperlink ref="M35" r:id="rId247" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N35" r:id="rId248"/>
-    <hyperlink ref="AW35" r:id="rId249" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
-    <hyperlink ref="C36" r:id="rId250" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="G36" r:id="rId251" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J36" r:id="rId252" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K36" r:id="rId253" tooltip="https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId254" tooltip="https://www.amazon.fr/dp/B0HBPKX2KK"/>
-    <hyperlink ref="M36" r:id="rId255" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N36" r:id="rId256"/>
-    <hyperlink ref="AW36" r:id="rId257" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
-    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
-    <hyperlink ref="K37" r:id="rId261" tooltip="https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="M37" r:id="rId263" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N37" r:id="rId264"/>
-    <hyperlink ref="AW37" r:id="rId265" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
-    <hyperlink ref="C38" r:id="rId266" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
-    <hyperlink ref="G38" r:id="rId267" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=dreame"/>
-    <hyperlink ref="J38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM?psc=1"/>
-    <hyperlink ref="K38" r:id="rId269" tooltip="https://m.media-amazon.com/images/I/31rbfP6p0aL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId270" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
+    <hyperlink ref="AW34" r:id="rId242" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
+    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K35" r:id="rId246" tooltip="https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0HBPKX2KK"/>
+    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N35" r:id="rId249"/>
+    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
+    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
+    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N36" r:id="rId257"/>
+    <hyperlink ref="AW36" r:id="rId258" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
+    <hyperlink ref="C37" r:id="rId259" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
+    <hyperlink ref="G37" r:id="rId260" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=dreame"/>
+    <hyperlink ref="J37" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM?psc=1"/>
+    <hyperlink ref="K37" r:id="rId262" tooltip="https://m.media-amazon.com/images/I/31rbfP6p0aL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0H3B6H4TM"/>
+    <hyperlink ref="M37" r:id="rId264" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N37" r:id="rId265"/>
+    <hyperlink ref="C38" r:id="rId266" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
+    <hyperlink ref="G38" r:id="rId267" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K38" r:id="rId269" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId270" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
     <hyperlink ref="M38" r:id="rId271" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N38" r:id="rId272"/>
-    <hyperlink ref="C39" r:id="rId273" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="G39" r:id="rId274" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J39" r:id="rId275" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K39" r:id="rId276" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId277" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="M39" r:id="rId278" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N39" r:id="rId279"/>
-    <hyperlink ref="AW39" r:id="rId280" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
-    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
-    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0HHNM96WW?psc=1"/>
-    <hyperlink ref="K40" r:id="rId284" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0HJR5CK76"/>
+    <hyperlink ref="AW38" r:id="rId273" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
+    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.fr/dp/B0HHNM96WW"/>
+    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0HHNM96WW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0HHNM96WW?psc=1"/>
+    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VvjQwJisL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0HJR5CK76"/>
+    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N39" r:id="rId280"/>
+    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K40" r:id="rId284" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41Md9nniqDL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
     <hyperlink ref="M40" r:id="rId286" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N40" r:id="rId287"/>
-    <hyperlink ref="C41" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="G41" r:id="rId289" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId290" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K41" r:id="rId291" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41Md9nniqDL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId292" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="M41" r:id="rId293" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N41" r:id="rId294"/>
-    <hyperlink ref="AW41" r:id="rId295" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C42" r:id="rId296" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G42" r:id="rId297" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId298" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K42" r:id="rId299" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId300" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="AW40" r:id="rId288" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C41" r:id="rId289" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G41" r:id="rId290" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K41" r:id="rId292" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="M41" r:id="rId294" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N41" r:id="rId295"/>
+    <hyperlink ref="C42" r:id="rId296" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G42" r:id="rId297" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId298" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K42" r:id="rId299" tooltip="https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId300" tooltip="https://www.amazon.fr/dp/B0DBJ2CJ2J"/>
     <hyperlink ref="M42" r:id="rId301" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N42" r:id="rId302"/>
-    <hyperlink ref="C43" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G43" r:id="rId304" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId305" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K43" r:id="rId306" tooltip="https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId307" tooltip="https://www.amazon.fr/dp/B0DBJ2CJ2J"/>
-    <hyperlink ref="M43" r:id="rId308" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N43" r:id="rId309"/>
-    <hyperlink ref="AW43" r:id="rId310" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C44" r:id="rId311" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="G44" r:id="rId312" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId313" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K44" r:id="rId314" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId315" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="M44" r:id="rId316" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N44" r:id="rId317"/>
-    <hyperlink ref="AW44" r:id="rId318" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
-    <hyperlink ref="C45" r:id="rId319" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
-    <hyperlink ref="G45" r:id="rId320" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=TWOPOINT"/>
-    <hyperlink ref="J45" r:id="rId321" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH?psc=1"/>
-    <hyperlink ref="K45" r:id="rId322" tooltip="https://m.media-amazon.com/images/I/41Iur5fvt1L._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId323" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
-    <hyperlink ref="M45" r:id="rId324" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N45" r:id="rId325"/>
-    <hyperlink ref="AW45" r:id="rId326" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5O6DZZGWMILN"/>
-    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.fr/dp/B0D2HFLM1C"/>
-    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.fr/dp/B0D2HFLM1C?psc=1"/>
-    <hyperlink ref="K46" r:id="rId330" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.fr/dp/B0DN6BPLYN"/>
+    <hyperlink ref="AW42" r:id="rId303" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C43" r:id="rId304" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="G43" r:id="rId305" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId306" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K43" r:id="rId307" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId308" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="M43" r:id="rId309" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N43" r:id="rId310"/>
+    <hyperlink ref="AW43" r:id="rId311" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
+    <hyperlink ref="C44" r:id="rId312" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
+    <hyperlink ref="G44" r:id="rId313" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=TWOPOINT"/>
+    <hyperlink ref="J44" r:id="rId314" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH?psc=1"/>
+    <hyperlink ref="K44" r:id="rId315" tooltip="https://m.media-amazon.com/images/I/41Iur5fvt1L._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId316" tooltip="https://www.amazon.fr/dp/B0HCN3FWXH"/>
+    <hyperlink ref="M44" r:id="rId317" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N44" r:id="rId318"/>
+    <hyperlink ref="AW44" r:id="rId319" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5O6DZZGWMILN"/>
+    <hyperlink ref="C45" r:id="rId320" tooltip="https://www.amazon.fr/dp/B0D2HFLM1C"/>
+    <hyperlink ref="G45" r:id="rId321" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId322" tooltip="https://www.amazon.fr/dp/B0D2HFLM1C?psc=1"/>
+    <hyperlink ref="K45" r:id="rId323" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId324" tooltip="https://www.amazon.fr/dp/B0DN6BPLYN"/>
+    <hyperlink ref="M45" r:id="rId325" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N45" r:id="rId326"/>
+    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
+    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH?psc=1"/>
+    <hyperlink ref="K46" r:id="rId330" tooltip="https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.fr/dp/B0HJW7LPHT"/>
     <hyperlink ref="M46" r:id="rId332" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N46" r:id="rId333"/>
-    <hyperlink ref="C47" r:id="rId334" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
-    <hyperlink ref="G47" r:id="rId335" tooltip="https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId336" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH?psc=1"/>
-    <hyperlink ref="K47" r:id="rId337" tooltip="https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId338" tooltip="https://www.amazon.fr/dp/B0HJW7LPHT"/>
-    <hyperlink ref="M47" r:id="rId339" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N47" r:id="rId340"/>
-    <hyperlink ref="AW47" r:id="rId341" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK"/>
-    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0F9XDVZ4N"/>
-    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NQILGDOH"/>
-    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.fr/dp/B0F9XDVZ4N?psc=1"/>
-    <hyperlink ref="K48" r:id="rId345" tooltip="https://m.media-amazon.com/images/I/31dfBZGIZML._SX600_SY600_CR,0,0,600,600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.fr/dp/B0F9XHDTPB"/>
-    <hyperlink ref="M48" r:id="rId347" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N48" r:id="rId348"/>
-    <hyperlink ref="AW48" r:id="rId349" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FTADH5UN7C2O"/>
-    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
-    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY?psc=1"/>
-    <hyperlink ref="K49" r:id="rId353" tooltip="https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
-    <hyperlink ref="M49" r:id="rId355" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N49" r:id="rId356"/>
-    <hyperlink ref="AW49" r:id="rId357" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
-    <hyperlink ref="C50" r:id="rId358" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR"/>
-    <hyperlink ref="G50" r:id="rId359" tooltip="https://www.amazon.frnull"/>
-    <hyperlink ref="J50" r:id="rId360" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR?psc=1"/>
-    <hyperlink ref="K50" r:id="rId361" tooltip="https://m.media-amazon.com/images/I/41JShjmKqDL._AC_US200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId362" tooltip="https://www.amazon.fr/dp/B0GY9WGM7P"/>
-    <hyperlink ref="M50" r:id="rId363" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N50" r:id="rId364"/>
-    <hyperlink ref="C51" r:id="rId365" tooltip="https://www.amazon.fr/dp/B0HFJG9Z8G"/>
-    <hyperlink ref="G51" r:id="rId366" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT"/>
-    <hyperlink ref="J51" r:id="rId367" tooltip="https://www.amazon.fr/dp/B0HFJG9Z8G?psc=1"/>
-    <hyperlink ref="K51" r:id="rId368" tooltip="https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId369" tooltip="https://www.amazon.fr/dp/B0HL67B91S"/>
-    <hyperlink ref="M51" r:id="rId370" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N51" r:id="rId371"/>
+    <hyperlink ref="AW46" r:id="rId334" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK"/>
+    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.fr/dp/B0F9XDVZ4N"/>
+    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NQILGDOH"/>
+    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.fr/dp/B0F9XDVZ4N?psc=1"/>
+    <hyperlink ref="K47" r:id="rId338" tooltip="https://m.media-amazon.com/images/I/31dfBZGIZML._SX600_SY600_CR,0,0,600,600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.fr/dp/B0F9XHDTPB"/>
+    <hyperlink ref="M47" r:id="rId340" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N47" r:id="rId341"/>
+    <hyperlink ref="AW47" r:id="rId342" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FTADH5UN7C2O"/>
+    <hyperlink ref="C48" r:id="rId343" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
+    <hyperlink ref="G48" r:id="rId344" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId345" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY?psc=1"/>
+    <hyperlink ref="K48" r:id="rId346" tooltip="https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId347" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
+    <hyperlink ref="M48" r:id="rId348" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N48" r:id="rId349"/>
+    <hyperlink ref="AW48" r:id="rId350" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
+    <hyperlink ref="C49" r:id="rId351" tooltip="https://www.amazon.fr/dp/B0HFJG9Z8G"/>
+    <hyperlink ref="G49" r:id="rId352" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT"/>
+    <hyperlink ref="J49" r:id="rId353" tooltip="https://www.amazon.fr/dp/B0HFJG9Z8G?psc=1"/>
+    <hyperlink ref="K49" r:id="rId354" tooltip="https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId355" tooltip="https://www.amazon.fr/dp/B0HL67B91S"/>
+    <hyperlink ref="M49" r:id="rId356" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N49" r:id="rId357"/>
   </hyperlinks>
-  <drawing r:id="rId372"/>
+  <drawing r:id="rId358"/>
 </worksheet>
 </file>
 
@@ -20931,18 +20376,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>15934</v>
+        <v>15597</v>
       </c>
       <c r="C2" s="15">
-        <v>1054511</v>
+        <v>1046089</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>66.17992971005397</v>
+        <v>67.06988523433994</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6848620304306714</v>
+        <v>0.6802302760696062</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20963,7 +20408,7 @@
         <v>129.815278647464</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06864093527035159</v>
+        <v>0.06964978847747394</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20984,7 +20429,7 @@
         <v>259.24632352941177</v>
       </c>
       <c r="G4" s="22">
-        <v>0.023381758789650132</v>
+        <v>0.023725413232151424</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21005,7 +20450,7 @@
         <v>110.6064453125</v>
       </c>
       <c r="G5" s="22">
-        <v>0.04401272242757672</v>
+        <v>0.044659601378167386</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21026,7 +20471,7 @@
         <v>55.6158315177923</v>
       </c>
       <c r="G6" s="22">
-        <v>0.0591850769363019</v>
+        <v>0.06005495224388329</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21047,7 +20492,7 @@
         <v>160.14417177914112</v>
       </c>
       <c r="G7" s="22">
-        <v>0.014011862804091807</v>
+        <v>0.014217802782502507</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21068,7 +20513,7 @@
         <v>218.13247863247864</v>
       </c>
       <c r="G8" s="22">
-        <v>0.010057594773489211</v>
+        <v>0.010205416721182782</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21089,7 +20534,7 @@
         <v>129.98859315589354</v>
       </c>
       <c r="G9" s="22">
-        <v>0.011304048826613943</v>
+        <v>0.011470190588337913</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21110,7 +20555,7 @@
         <v>99.90196078431373</v>
       </c>
       <c r="G10" s="22">
-        <v>0.0087681595461188</v>
+        <v>0.008897029962056784</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21131,7 +20576,7 @@
         <v>75.99148936170212</v>
       </c>
       <c r="G11" s="22">
-        <v>0.010100575947734893</v>
+        <v>0.010249029613153647</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21152,7 +20597,7 @@
         <v>73.52479338842976</v>
       </c>
       <c r="G12" s="22">
-        <v>0.010401444167454655</v>
+        <v>0.010554319856949714</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21173,7 +20618,7 @@
         <v>134.98850574712642</v>
       </c>
       <c r="G13" s="22">
-        <v>0.003739362159374194</v>
+        <v>0.0037943216014653934</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21194,7 +20639,7 @@
         <v>28.639240506329113</v>
       </c>
       <c r="G14" s="22">
-        <v>0.013582051061635004</v>
+        <v>0.013781673862793841</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21215,7 +20660,7 @@
         <v>54.82258064516129</v>
       </c>
       <c r="G15" s="22">
-        <v>0.005329665606464368</v>
+        <v>0.0054079986043874565</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21236,7 +20681,7 @@
         <v>73.72527472527473</v>
       </c>
       <c r="G16" s="22">
-        <v>0.003911286856356916</v>
+        <v>0.00396877316934886</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21257,7 +20702,7 @@
         <v>28.398104265402843</v>
       </c>
       <c r="G17" s="22">
-        <v>0.009069027765838563</v>
+        <v>0.00920232020585285</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21278,7 +20723,7 @@
         <v>149.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0017192469698272157</v>
+        <v>0.0017445156788346635</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21299,7 +20744,7 @@
         <v>65.98823529411764</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0036533998108828334</v>
+        <v>0.00370709581752366</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21320,7 +20765,7 @@
         <v>79.98484848484848</v>
       </c>
       <c r="G20" s="22">
-        <v>0.002836757500214906</v>
+        <v>0.002878450870077195</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21341,7 +20786,7 @@
         <v>99.98076923076923</v>
       </c>
       <c r="G21" s="22">
-        <v>0.00223502106077538</v>
+        <v>0.0022678703824850627</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21362,7 +20807,7 @@
         <v>64.8961038961039</v>
       </c>
       <c r="G22" s="22">
-        <v>0.00330955041691739</v>
+        <v>0.0033581926817567273</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21383,7 +20828,7 @@
         <v>69.95652173913044</v>
       </c>
       <c r="G23" s="22">
-        <v>0.002965701022951947</v>
+        <v>0.0030092895459897947</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21404,7 +20849,7 @@
         <v>80.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0020630963637926587</v>
+        <v>0.0020934188146015963</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21425,7 +20870,7 @@
         <v>39.9</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0008596234849136079</v>
+        <v>0.0008722578394173317</v>
       </c>
     </row>
   </sheetData>
@@ -21489,18 +20934,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>19480</v>
+        <v>19143</v>
       </c>
       <c r="C2" s="15">
-        <v>1573150</v>
+        <v>1564728</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>80.75718685831622</v>
+        <v>81.73891239617615</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8372732743058541</v>
+        <v>0.8348815909982991</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21521,7 +20966,7 @@
         <v>55.6158315177923</v>
       </c>
       <c r="G3" s="22">
-        <v>0.0591850769363019</v>
+        <v>0.06005495224388329</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21542,7 +20987,7 @@
         <v>159.99065420560748</v>
       </c>
       <c r="G4" s="22">
-        <v>0.013796956932863405</v>
+        <v>0.013999738322648175</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21563,7 +21008,7 @@
         <v>129.98859315589354</v>
       </c>
       <c r="G5" s="22">
-        <v>0.011304048826613943</v>
+        <v>0.011470190588337913</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21584,7 +21029,7 @@
         <v>99.90196078431373</v>
       </c>
       <c r="G6" s="22">
-        <v>0.0087681595461188</v>
+        <v>0.008897029962056784</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21605,7 +21050,7 @@
         <v>75.99148936170212</v>
       </c>
       <c r="G7" s="22">
-        <v>0.010100575947734893</v>
+        <v>0.010249029613153647</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21626,7 +21071,7 @@
         <v>73.52479338842976</v>
       </c>
       <c r="G8" s="22">
-        <v>0.010401444167454655</v>
+        <v>0.010554319856949714</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21647,7 +21092,7 @@
         <v>239.16</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0021490587122840197</v>
+        <v>0.0021806445985433293</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21668,7 +21113,7 @@
         <v>134.98850574712642</v>
       </c>
       <c r="G10" s="22">
-        <v>0.003739362159374194</v>
+        <v>0.0037943216014653934</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21689,7 +21134,7 @@
         <v>28.639240506329113</v>
       </c>
       <c r="G11" s="22">
-        <v>0.013582051061635004</v>
+        <v>0.013781673862793841</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21710,7 +21155,7 @@
         <v>72.183908045977</v>
       </c>
       <c r="G12" s="22">
-        <v>0.003739362159374194</v>
+        <v>0.0037943216014653934</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21731,7 +21176,7 @@
         <v>28.398104265402843</v>
       </c>
       <c r="G13" s="22">
-        <v>0.009069027765838563</v>
+        <v>0.00920232020585285</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21752,7 +21197,7 @@
         <v>65.98823529411764</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0036533998108828334</v>
+        <v>0.00370709581752366</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21773,7 +21218,7 @@
         <v>99.98076923076923</v>
       </c>
       <c r="G15" s="22">
-        <v>0.00223502106077538</v>
+        <v>0.0022678703824850627</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21794,7 +21239,7 @@
         <v>64.8961038961039</v>
       </c>
       <c r="G16" s="22">
-        <v>0.00330955041691739</v>
+        <v>0.0033581926817567273</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21815,7 +21260,7 @@
         <v>69.95652173913044</v>
       </c>
       <c r="G17" s="22">
-        <v>0.002965701022951947</v>
+        <v>0.0030092895459897947</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21836,7 +21281,7 @@
         <v>80.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0020630963637926587</v>
+        <v>0.0020934188146015963</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21857,7 +21302,7 @@
         <v>170.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.00021490587122840197</v>
+        <v>0.00021806445985433293</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21878,7 +21323,7 @@
         <v>39.9</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0008596234849136079</v>
+        <v>0.0008722578394173317</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21899,7 +21344,7 @@
         <v>14.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0015903034470901745</v>
+        <v>0.0016136770029220638</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
